--- a/data/proteomics/organell_protein_volume_tao2.xlsx
+++ b/data/proteomics/organell_protein_volume_tao2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK9"/>
+  <dimension ref="A1:EM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,6 +1129,16 @@
           <t>sample_ID</t>
         </is>
       </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>total_pro_volume</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1556,6 +1566,14 @@
       <c r="EK2" t="n">
         <v>5</v>
       </c>
+      <c r="EL2" t="n">
+        <v>1.912475495650298</v>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>C-lim rep1 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1983,6 +2001,14 @@
       <c r="EK3" t="n">
         <v>5</v>
       </c>
+      <c r="EL3" t="n">
+        <v>1.967840779985522</v>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>C-lim rep2 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2410,6 +2436,14 @@
       <c r="EK4" t="n">
         <v>115</v>
       </c>
+      <c r="EL4" t="n">
+        <v>0.9861729177512535</v>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>C/N=115 rep1 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2837,6 +2871,14 @@
       <c r="EK5" t="n">
         <v>115</v>
       </c>
+      <c r="EL5" t="n">
+        <v>1.127757767916389</v>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>C/N=115 rep2 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -3264,6 +3306,14 @@
       <c r="EK6" t="n">
         <v>30</v>
       </c>
+      <c r="EL6" t="n">
+        <v>1.488678410143015</v>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>C/N=30 rep1 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -3691,6 +3741,14 @@
       <c r="EK7" t="n">
         <v>30</v>
       </c>
+      <c r="EL7" t="n">
+        <v>1.520156369982094</v>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>C/N=30 rep2 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4118,6 +4176,14 @@
       <c r="EK8" t="n">
         <v>50</v>
       </c>
+      <c r="EL8" t="n">
+        <v>0.8921217673791332</v>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>C/N=50 rep1 prot (fmol mgDW-1)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4544,6 +4610,14 @@
       </c>
       <c r="EK9" t="n">
         <v>50</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.9292315671910052</v>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>C/N=50 rep2 prot (fmol mgDW-1)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/proteomics/organell_protein_volume_tao2.xlsx
+++ b/data/proteomics/organell_protein_volume_tao2.xlsx
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7206766012475401</v>
+        <v>0.7206766012475397</v>
       </c>
       <c r="C2" t="n">
         <v>0.002165212380823581</v>
@@ -1159,13 +1159,13 @@
         <v>0.0534906314377176</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2759418730875776</v>
+        <v>0.2759418730875773</v>
       </c>
       <c r="G2" t="n">
         <v>1.026677773232596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2933550807927052</v>
+        <v>0.2933550807927053</v>
       </c>
       <c r="I2" t="n">
         <v>0.01878197683417896</v>
@@ -1177,28 +1177,28 @@
         <v>0.01417496949717756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07504183978345617</v>
+        <v>0.07504183978345613</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007410358115722398</v>
+        <v>0.007410358115722399</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03172569423987595</v>
+        <v>0.03172569423987596</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0061984645466961</v>
+        <v>0.006198464546696099</v>
       </c>
       <c r="P2" t="n">
         <v>0.01641634096772068</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.005810748897010688</v>
+        <v>0.004967979449627478</v>
       </c>
       <c r="R2" t="n">
         <v>0.0113377798648723</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01041929992239055</v>
+        <v>0.01041929992239056</v>
       </c>
       <c r="T2" t="n">
         <v>0.03206229630425289</v>
@@ -1210,25 +1210,25 @@
         <v>0.002668762731131356</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02718682175248842</v>
+        <v>0.02718682175248843</v>
       </c>
       <c r="X2" t="n">
         <v>0.0003656975943547267</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.005314854279585014</v>
+        <v>0.005314854279585013</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008584899219846098</v>
+        <v>0.0085848992198461</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03892445205620823</v>
+        <v>0.03892445205620821</v>
       </c>
       <c r="AB2" t="n">
         <v>0.002104212287918602</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0547245181687482</v>
+        <v>0.05472451816874817</v>
       </c>
       <c r="AD2" t="n">
         <v>0.000120357173627712</v>
@@ -1237,19 +1237,19 @@
         <v>5.507364114259175e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08874967499681234</v>
+        <v>0.08874967499681236</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03486329942636326</v>
+        <v>0.03486329942636325</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.004775703665474899</v>
+        <v>0.0047757036654749</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.00138577074501759</v>
+        <v>0.001385770745017591</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.004825647692773465</v>
+        <v>0.004825647692773463</v>
       </c>
       <c r="AK2" t="n">
         <v>0.03385765157792101</v>
@@ -1258,19 +1258,19 @@
         <v>0.003121523624958098</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0006026690997658103</v>
+        <v>0.0006026690997658102</v>
       </c>
       <c r="AN2" t="n">
         <v>0.0003594892964050996</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001985371456696077</v>
+        <v>0.001985371456696078</v>
       </c>
       <c r="AP2" t="n">
         <v>0.001504528918223736</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.004687852375112364</v>
+        <v>0.004687852375112363</v>
       </c>
       <c r="AR2" t="n">
         <v>0.01039381494161817</v>
@@ -1279,7 +1279,7 @@
         <v>8.071701180739867e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0004233345722119059</v>
+        <v>0.0004233345722119058</v>
       </c>
       <c r="AU2" t="n">
         <v>0.0005314101706905116</v>
@@ -1294,16 +1294,16 @@
         <v>0.003408458254454325</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.09772824350641911</v>
+        <v>0.09772824350641907</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0009845292239379119</v>
+        <v>0.0009845292239379121</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.0005060412189208479</v>
+        <v>0.000506041218920848</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05058979606964793</v>
+        <v>0.05058979606964792</v>
       </c>
       <c r="BC2" t="n">
         <v>0.01692564880503614</v>
@@ -1315,7 +1315,7 @@
         <v>0.002276368382593859</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.002411484928312957</v>
+        <v>0.002411484928312958</v>
       </c>
       <c r="BG2" t="n">
         <v>0.003472351442984559</v>
@@ -1324,13 +1324,13 @@
         <v>0.01249855510780769</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0006521834794809146</v>
+        <v>0.0006521834794809147</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.001917763204470912</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01427705614429742</v>
+        <v>0.01427705614429741</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0002648996720415359</v>
@@ -1345,7 +1345,7 @@
         <v>0.0001397935434013381</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0007152548367379151</v>
+        <v>0.000715254836737915</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.0009558292781177678</v>
@@ -1363,16 +1363,16 @@
         <v>0.0100282649034211</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.00603891971156402</v>
+        <v>0.006038919711564021</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.707726353755101e-05</v>
+        <v>5.7077263537551e-05</v>
       </c>
       <c r="BX2" t="n">
         <v>0.003008266286336013</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.000897288807022471</v>
+        <v>0.0008972888070224709</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.0009400126599844494</v>
@@ -1387,7 +1387,7 @@
         <v>0.0003458744746313962</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0007543857748958558</v>
+        <v>0.0007543857748958557</v>
       </c>
       <c r="CE2" t="n">
         <v>0.005894623447802896</v>
@@ -1423,13 +1423,13 @@
         <v>0.001558142153535212</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.00322223055018087</v>
+        <v>0.003222230550180869</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.004407527250484313</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.0009454334886373938</v>
+        <v>0.000945433488637394</v>
       </c>
       <c r="CS2" t="n">
         <v>0.0003819449009389856</v>
@@ -1444,10 +1444,10 @@
         <v>0.001030023573464819</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.0008004529009153199</v>
+        <v>0.0008004529009153198</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.005335446337837006</v>
+        <v>0.005335446337837007</v>
       </c>
       <c r="CY2" t="n">
         <v>0.0004332048033900891</v>
@@ -1456,10 +1456,10 @@
         <v>0.0009076561191933141</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0008479698973287357</v>
+        <v>0.0008479698973287356</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0009516361400175823</v>
+        <v>0.0009516361400175822</v>
       </c>
       <c r="DC2" t="n">
         <v>9.690740714235118e-05</v>
@@ -1492,16 +1492,16 @@
         <v>0.0005254078033417433</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0004162760449542364</v>
+        <v>0.0004162760449542365</v>
       </c>
       <c r="DN2" t="n">
         <v>9.506134334105387e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.004675262105543024</v>
+        <v>0.004675262105543023</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2018002370698955</v>
+        <v>0.2018002370698954</v>
       </c>
       <c r="DQ2" t="n">
         <v>8.510981947950737e-05</v>
@@ -1510,7 +1510,7 @@
         <v>0.0002027411895147917</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.003881988100938986</v>
+        <v>0.003881988100938987</v>
       </c>
       <c r="DT2" t="n">
         <v>0.003270992941904004</v>
@@ -1531,19 +1531,19 @@
         <v>0.0004115641595516574</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0009297940886889616</v>
+        <v>0.0009297940886889617</v>
       </c>
       <c r="EA2" t="n">
         <v>0.001284530472416466</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0008440254103115964</v>
+        <v>0.0008440254103115965</v>
       </c>
       <c r="EC2" t="n">
         <v>0.02641732976563713</v>
       </c>
       <c r="ED2" t="n">
-        <v>7.913513099012433e-05</v>
+        <v>7.913513099012431e-05</v>
       </c>
       <c r="EE2" t="n">
         <v>0.0006058516037838339</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7486753180912473</v>
+        <v>0.7486753180912479</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002597865343457151</v>
+        <v>0.00259786534345715</v>
       </c>
       <c r="D3" t="n">
         <v>0.003202166869715695</v>
@@ -1594,16 +1594,16 @@
         <v>0.06076809088901151</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2969670994072943</v>
+        <v>0.2969670994072937</v>
       </c>
       <c r="G3" t="n">
-        <v>1.027783529499928</v>
+        <v>1.027783529499927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333292210088032</v>
+        <v>0.3332922100880313</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02504158188918004</v>
+        <v>0.02504158188918005</v>
       </c>
       <c r="J3" t="n">
         <v>0.0387051002436261</v>
@@ -1612,7 +1612,7 @@
         <v>0.01791084159389123</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08137628231289799</v>
+        <v>0.08137628231289801</v>
       </c>
       <c r="M3" t="n">
         <v>0.007628478768137784</v>
@@ -1621,13 +1621,13 @@
         <v>0.03506363152408568</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006951105782700875</v>
+        <v>0.006951105782700873</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01854546805473341</v>
+        <v>0.01854546805473342</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00672299825750231</v>
+        <v>0.005839857338368132</v>
       </c>
       <c r="R3" t="n">
         <v>0.01312849779840527</v>
@@ -1645,16 +1645,16 @@
         <v>0.002875072698842628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02845654439413755</v>
+        <v>0.02845654439413756</v>
       </c>
       <c r="X3" t="n">
         <v>0.0004125956048767483</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.006021808482208383</v>
+        <v>0.006021808482208379</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009614938255542717</v>
+        <v>0.009614938255542715</v>
       </c>
       <c r="AA3" t="n">
         <v>0.03996716207904129</v>
@@ -1663,34 +1663,34 @@
         <v>0.00237217221774785</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.06009954207393831</v>
+        <v>0.06009954207393826</v>
       </c>
       <c r="AD3" t="n">
         <v>0.0001317697807861838</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.774399582133144e-05</v>
+        <v>5.774399582133145e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09767290382095489</v>
+        <v>0.09767290382095491</v>
       </c>
       <c r="AG3" t="n">
         <v>0.03539739824581133</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.005216149023496733</v>
+        <v>0.005216149023496734</v>
       </c>
       <c r="AI3" t="n">
         <v>0.001439201850859847</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.005496880009575861</v>
+        <v>0.005496880009575862</v>
       </c>
       <c r="AK3" t="n">
         <v>0.03819211174009295</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.003624242152922136</v>
+        <v>0.003624242152922135</v>
       </c>
       <c r="AM3" t="n">
         <v>0.0006814567443603864</v>
@@ -1699,7 +1699,7 @@
         <v>0.0004522633937595655</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.002290392726018871</v>
+        <v>0.00229039272601887</v>
       </c>
       <c r="AP3" t="n">
         <v>0.001786713449581035</v>
@@ -1723,25 +1723,25 @@
         <v>0.004555935788711944</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02838269721690987</v>
+        <v>0.02838269721690988</v>
       </c>
       <c r="AX3" t="n">
         <v>0.003459714322852356</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.09990705848076041</v>
+        <v>0.0999070584807604</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.00105782130834454</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0005714311666559038</v>
+        <v>0.0005714311666559039</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.05230889568489661</v>
+        <v>0.0523088956848966</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.01966568678614984</v>
+        <v>0.01966568678614985</v>
       </c>
       <c r="BD3" t="n">
         <v>0.03586324812332643</v>
@@ -1750,7 +1750,7 @@
         <v>0.002663899499940106</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.002762929072621569</v>
+        <v>0.00276292907262157</v>
       </c>
       <c r="BG3" t="n">
         <v>0.003732412503245876</v>
@@ -1759,13 +1759,13 @@
         <v>0.01228235136643472</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.000758400420530343</v>
+        <v>0.0007584004205303428</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.001822310239093187</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01530153396880905</v>
+        <v>0.01530153396880906</v>
       </c>
       <c r="BL3" t="n">
         <v>0.0002767092505913733</v>
@@ -1780,16 +1780,16 @@
         <v>0.0001470032871991947</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0008054907830582275</v>
+        <v>0.0008054907830582276</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0009645009173305681</v>
+        <v>0.0009645009173305685</v>
       </c>
       <c r="BR3" t="n">
         <v>0.001481836520397154</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.01501492120747815</v>
+        <v>0.01501492120747816</v>
       </c>
       <c r="BT3" t="n">
         <v>0.00838897409911929</v>
@@ -1798,10 +1798,10 @@
         <v>0.01135150157225728</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.006928577250794114</v>
+        <v>0.006928577250794115</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.704664523449579e-05</v>
+        <v>6.704664523449581e-05</v>
       </c>
       <c r="BX3" t="n">
         <v>0.003326500246901522</v>
@@ -1813,7 +1813,7 @@
         <v>0.001504333596607258</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0005039652044605498</v>
+        <v>0.0005039652044605499</v>
       </c>
       <c r="CB3" t="n">
         <v>0.0006297246876554948</v>
@@ -1861,25 +1861,25 @@
         <v>0.003639869019038072</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.004769436485694282</v>
+        <v>0.004769436485694281</v>
       </c>
       <c r="CR3" t="n">
         <v>0.0009321793608618741</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.0003828535351421671</v>
+        <v>0.000382853535142167</v>
       </c>
       <c r="CT3" t="n">
         <v>0.001230525026507763</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0009719515649993998</v>
+        <v>0.0009719515649993997</v>
       </c>
       <c r="CV3" t="n">
         <v>0.001073794422543585</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0008624287186771864</v>
+        <v>0.0008624287186771865</v>
       </c>
       <c r="CX3" t="n">
         <v>0.007174601744675881</v>
@@ -1888,10 +1888,10 @@
         <v>0.000470425138479064</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0009451472449842708</v>
+        <v>0.000945147244984271</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.001090625075925171</v>
+        <v>0.001090625075925172</v>
       </c>
       <c r="DB3" t="n">
         <v>0.001062699577284428</v>
@@ -1900,7 +1900,7 @@
         <v>0.0001022315132066139</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.004527948733535525</v>
+        <v>0.004527948733535526</v>
       </c>
       <c r="DE3" t="n">
         <v>0.0003528890617523331</v>
@@ -1924,7 +1924,7 @@
         <v>0.003928713270743762</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0006347014435179152</v>
+        <v>0.0006347014435179151</v>
       </c>
       <c r="DM3" t="n">
         <v>0.0007232973569852989</v>
@@ -1933,10 +1933,10 @@
         <v>8.659826124874666e-05</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.005199894661483802</v>
+        <v>0.005199894661483803</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.1954248287620581</v>
+        <v>0.1954248287620582</v>
       </c>
       <c r="DQ3" t="n">
         <v>9.24848858154068e-05</v>
@@ -1957,19 +1957,19 @@
         <v>0.0016305727947586</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.002166604134880089</v>
+        <v>0.002166604134880088</v>
       </c>
       <c r="DX3" t="n">
         <v>0.002157031193510175</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0004277224429845475</v>
+        <v>0.0004277224429845476</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.001064057079870107</v>
+        <v>0.001064057079870106</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.001197708058567182</v>
+        <v>0.001197708058567181</v>
       </c>
       <c r="EB3" t="n">
         <v>0.000958419526520414</v>
@@ -1981,10 +1981,10 @@
         <v>6.969093161849942e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.0006421344235611171</v>
+        <v>0.0006421344235611172</v>
       </c>
       <c r="EF3" t="n">
-        <v>5.01764243257681e-05</v>
+        <v>5.017642432576809e-05</v>
       </c>
       <c r="EG3" t="n">
         <v>0.0003624058409577877</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3430553657108146</v>
+        <v>0.3430553657108142</v>
       </c>
       <c r="C4" t="n">
         <v>0.000885670438494863</v>
@@ -2029,13 +2029,13 @@
         <v>0.03823944859638725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1675448549038019</v>
+        <v>0.1675448549038018</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5177130940050537</v>
+        <v>0.5177130940050545</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1803172662575533</v>
+        <v>0.1803172662575532</v>
       </c>
       <c r="I4" t="n">
         <v>0.01326588465130503</v>
@@ -2044,13 +2044,13 @@
         <v>0.02704253700713397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007755983548600882</v>
+        <v>0.007755983548600881</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04148637488097953</v>
+        <v>0.04148637488097948</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009848290384017978</v>
+        <v>0.009848290384017975</v>
       </c>
       <c r="N4" t="n">
         <v>0.02020569778623052</v>
@@ -2059,19 +2059,19 @@
         <v>0.002961602000507267</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01000549589439205</v>
+        <v>0.01000549589439204</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.009374639697651725</v>
+        <v>0.002388290622986099</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005301905166709757</v>
+        <v>0.005301905166709754</v>
       </c>
       <c r="S4" t="n">
         <v>0.005679545102279857</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01592194300676974</v>
+        <v>0.01592194300676973</v>
       </c>
       <c r="U4" t="n">
         <v>9.757264860685046e-05</v>
@@ -2083,22 +2083,22 @@
         <v>0.01464827675648381</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001326931324769749</v>
+        <v>0.0001326931324769748</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003620375266243746</v>
+        <v>0.003620375266243745</v>
       </c>
       <c r="Z4" t="n">
         <v>0.003599326927027622</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02252219665124337</v>
+        <v>0.02252219665124339</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0009652623038228178</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04394894672626476</v>
+        <v>0.04394894672626477</v>
       </c>
       <c r="AD4" t="n">
         <v>5.775459849322818e-05</v>
@@ -2116,10 +2116,10 @@
         <v>0.002281141284806587</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001176488845484317</v>
+        <v>0.001176488845484316</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002241453029249024</v>
+        <v>0.002241453029249023</v>
       </c>
       <c r="AK4" t="n">
         <v>0.01883392801411436</v>
@@ -2143,7 +2143,7 @@
         <v>0.003981141013338681</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005668030634599567</v>
+        <v>0.00566803063459957</v>
       </c>
       <c r="AS4" t="n">
         <v>5.398288266629993e-05</v>
@@ -2161,25 +2161,25 @@
         <v>0.03262201908569498</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001229400162593731</v>
+        <v>0.00122940016259373</v>
       </c>
       <c r="AY4" t="n">
         <v>0.04532951408041016</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.000753286440825153</v>
+        <v>0.0007532864408251531</v>
       </c>
       <c r="BA4" t="n">
         <v>0.0002464561791329419</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03478727565652048</v>
+        <v>0.03478727565652049</v>
       </c>
       <c r="BC4" t="n">
         <v>0.01263737092296079</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01299179214273111</v>
+        <v>0.0129917921427311</v>
       </c>
       <c r="BE4" t="n">
         <v>0.001376486495565132</v>
@@ -2200,13 +2200,13 @@
         <v>0.0007646601323309712</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.008520284899173154</v>
+        <v>0.00852028489917315</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0002145544103420147</v>
+        <v>0.0002145544103420148</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03146769602962319</v>
+        <v>0.0314676960296232</v>
       </c>
       <c r="BN4" t="n">
         <v>0.001802805041483812</v>
@@ -2218,7 +2218,7 @@
         <v>0.0005157270914584792</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0007993134266321579</v>
+        <v>0.0007993134266321578</v>
       </c>
       <c r="BR4" t="n">
         <v>0.0007198732219163446</v>
@@ -2230,7 +2230,7 @@
         <v>0.004608654807769026</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005097165407296869</v>
+        <v>0.005097165407296868</v>
       </c>
       <c r="BV4" t="n">
         <v>0.004514360845371798</v>
@@ -2254,7 +2254,7 @@
         <v>0.0003606024759123209</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0001985093429768793</v>
+        <v>0.0001985093429768792</v>
       </c>
       <c r="CD4" t="n">
         <v>0.0002691150262251733</v>
@@ -2266,7 +2266,7 @@
         <v>0.001268940738589457</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0074231960933362</v>
+        <v>0.007423196093336201</v>
       </c>
       <c r="CH4" t="n">
         <v>0.0008008417200567042</v>
@@ -2287,7 +2287,7 @@
         <v>3.910870831313591e-05</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0002980921813080965</v>
+        <v>0.0002980921813080964</v>
       </c>
       <c r="CO4" t="n">
         <v>0.001021236852469434</v>
@@ -2299,13 +2299,13 @@
         <v>0.001060361338752975</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0005463163359374085</v>
+        <v>0.0005463163359374083</v>
       </c>
       <c r="CS4" t="n">
         <v>0.0001321732813335232</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0005327976803238159</v>
+        <v>0.0005327976803238158</v>
       </c>
       <c r="CU4" t="n">
         <v>0.0003570838860867273</v>
@@ -2314,7 +2314,7 @@
         <v>0.0007036499146164394</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0002805955961664153</v>
+        <v>0.0002805955961664154</v>
       </c>
       <c r="CX4" t="n">
         <v>0.003905950851010232</v>
@@ -2323,19 +2323,19 @@
         <v>0.0001731836886829889</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.00038087406270667</v>
+        <v>0.0003808740627066699</v>
       </c>
       <c r="DA4" t="n">
         <v>0.0007730822927595244</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0006490893475185471</v>
+        <v>0.0006490893475185472</v>
       </c>
       <c r="DC4" t="n">
         <v>8.429344223720198e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.003227950362975371</v>
+        <v>0.003227950362975373</v>
       </c>
       <c r="DE4" t="n">
         <v>0.0001203861095603063</v>
@@ -2350,7 +2350,7 @@
         <v>0.00132538947282932</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001503245223312975</v>
+        <v>0.0001503245223312976</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.0002435989733140792</v>
@@ -2362,7 +2362,7 @@
         <v>0.0003068044028996069</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0005035210007240595</v>
+        <v>0.0005035210007240594</v>
       </c>
       <c r="DN4" t="n">
         <v>5.40724381267699e-05</v>
@@ -2383,16 +2383,16 @@
         <v>0.001805032512959296</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0009571892435833396</v>
+        <v>0.0009571892435833397</v>
       </c>
       <c r="DU4" t="n">
         <v>0.0021111026128303</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0005294244760161971</v>
+        <v>0.0005294244760161973</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0008761793978261823</v>
+        <v>0.0008761793978261822</v>
       </c>
       <c r="DX4" t="n">
         <v>0.0008286565291732521</v>
@@ -2404,7 +2404,7 @@
         <v>0.0003456426315875525</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0006487622394404828</v>
+        <v>0.000648762239440483</v>
       </c>
       <c r="EB4" t="n">
         <v>0.0004162119096121748</v>
@@ -2425,7 +2425,7 @@
         <v>0.000235351232176808</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.871733344609492e-05</v>
+        <v>8.871733344609494e-05</v>
       </c>
       <c r="EI4" t="n">
         <v>6.472961012042393e-05</v>
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.401928515486453</v>
+        <v>0.4019285154864529</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001692658949330429</v>
+        <v>0.001692658949330428</v>
       </c>
       <c r="D5" t="n">
         <v>0.002127359910725046</v>
@@ -2464,16 +2464,16 @@
         <v>0.04583402489824994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2067008651660894</v>
+        <v>0.2067008651660895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.561023148397389</v>
+        <v>0.5610231483973882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.216857586251848</v>
+        <v>0.2168575862518479</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01809708790491718</v>
+        <v>0.01809708790491719</v>
       </c>
       <c r="J5" t="n">
         <v>0.03948225734603457</v>
@@ -2482,13 +2482,13 @@
         <v>0.01397022867435818</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06133125873541263</v>
+        <v>0.06133125873541262</v>
       </c>
       <c r="M5" t="n">
         <v>0.01536358712727088</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0226561517636389</v>
+        <v>0.02265615176363889</v>
       </c>
       <c r="O5" t="n">
         <v>0.002618007595985778</v>
@@ -2497,16 +2497,16 @@
         <v>0.01460750202411441</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01508986529448601</v>
+        <v>0.003636754291032936</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008551162770785039</v>
+        <v>0.008551162770785038</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00830831560006192</v>
+        <v>0.008308315600061919</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02661502244646363</v>
+        <v>0.02661502244646362</v>
       </c>
       <c r="U5" t="n">
         <v>0.0001831603106425639</v>
@@ -2518,10 +2518,10 @@
         <v>0.01689654526829179</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002630559794953422</v>
+        <v>0.0002630559794953423</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003920830544407506</v>
+        <v>0.003920830544407507</v>
       </c>
       <c r="Z5" t="n">
         <v>0.005801334335250112</v>
@@ -2536,19 +2536,19 @@
         <v>0.06886937735103742</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.441716504666133e-05</v>
+        <v>7.441716504666132e-05</v>
       </c>
       <c r="AE5" t="n">
         <v>3.856991155758002e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05681907896462444</v>
+        <v>0.05681907896462441</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03336788588497681</v>
+        <v>0.03336788588497682</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003439969001883048</v>
+        <v>0.003439969001883047</v>
       </c>
       <c r="AI5" t="n">
         <v>0.001277485236306388</v>
@@ -2578,43 +2578,43 @@
         <v>0.004223869516288714</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.007457918265478387</v>
+        <v>0.007457918265478389</v>
       </c>
       <c r="AS5" t="n">
         <v>7.149656626823477e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0004076070836833262</v>
+        <v>0.0004076070836833261</v>
       </c>
       <c r="AU5" t="n">
         <v>0.0004501973381811802</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003065631267060558</v>
+        <v>0.003065631267060559</v>
       </c>
       <c r="AW5" t="n">
         <v>0.0220561062127763</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001482569438582716</v>
+        <v>0.001482569438582717</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.04242332322754327</v>
+        <v>0.04242332322754325</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0009237582461756401</v>
+        <v>0.0009237582461756403</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0003504341656519025</v>
+        <v>0.0003504341656519024</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04970071869356308</v>
+        <v>0.04970071869356309</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0169903481431923</v>
+        <v>0.01699034814319229</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01423237506602249</v>
+        <v>0.0142323750660225</v>
       </c>
       <c r="BE5" t="n">
         <v>0.001968871332883028</v>
@@ -2623,7 +2623,7 @@
         <v>0.001938598779796693</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.002105809709764581</v>
+        <v>0.00210580970976458</v>
       </c>
       <c r="BH5" t="n">
         <v>0.0120967276360296</v>
@@ -2650,7 +2650,7 @@
         <v>0.0001318629113914031</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0006623592011591602</v>
+        <v>0.0006623592011591605</v>
       </c>
       <c r="BQ5" t="n">
         <v>0.0009088260020386009</v>
@@ -2665,13 +2665,13 @@
         <v>0.00609738541870462</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.006388019538184301</v>
+        <v>0.006388019538184302</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.005457372397157168</v>
+        <v>0.005457372397157169</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.16939084226961e-05</v>
+        <v>4.169390842269611e-05</v>
       </c>
       <c r="BX5" t="n">
         <v>0.002080663635046062</v>
@@ -2686,7 +2686,7 @@
         <v>0.0002977600190888229</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.0005591171342998267</v>
+        <v>0.0005591171342998268</v>
       </c>
       <c r="CC5" t="n">
         <v>0.0002023102024598411</v>
@@ -2713,7 +2713,7 @@
         <v>0.01995775802250916</v>
       </c>
       <c r="CK5" t="n">
-        <v>5.841268462430141e-05</v>
+        <v>5.84126846243014e-05</v>
       </c>
       <c r="CL5" t="n">
         <v>0.001846873854393551</v>
@@ -2722,7 +2722,7 @@
         <v>6.473508601487339e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004739921332973539</v>
+        <v>0.0004739921332973538</v>
       </c>
       <c r="CO5" t="n">
         <v>0.0007008468417436651</v>
@@ -2752,7 +2752,7 @@
         <v>0.000518748103453611</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004945121414306792</v>
+        <v>0.004945121414306791</v>
       </c>
       <c r="CY5" t="n">
         <v>0.0002425502502102747</v>
@@ -2770,7 +2770,7 @@
         <v>6.605602595483235e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.003102586280055811</v>
+        <v>0.00310258628005581</v>
       </c>
       <c r="DE5" t="n">
         <v>0.000192282630077617</v>
@@ -2797,7 +2797,7 @@
         <v>0.0004506958442220006</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0008976703429479455</v>
+        <v>0.0008976703429479456</v>
       </c>
       <c r="DN5" t="n">
         <v>5.830078129464113e-05</v>
@@ -2806,16 +2806,16 @@
         <v>0.00261247536931393</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.09524181228279197</v>
+        <v>0.09524181228279194</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.758540001701814e-05</v>
+        <v>3.758540001701815e-05</v>
       </c>
       <c r="DR5" t="n">
         <v>0.0001517251283875759</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00217946393691283</v>
+        <v>0.002179463936912829</v>
       </c>
       <c r="DT5" t="n">
         <v>0.001685883609836578</v>
@@ -2839,16 +2839,16 @@
         <v>0.0005046834998789431</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0005956865563841977</v>
+        <v>0.0005956865563841978</v>
       </c>
       <c r="EB5" t="n">
         <v>0.000612509162358934</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.01540454056417115</v>
+        <v>0.01540454056417116</v>
       </c>
       <c r="ED5" t="n">
-        <v>4.110998198040895e-05</v>
+        <v>4.110998198040894e-05</v>
       </c>
       <c r="EE5" t="n">
         <v>0.0001490778114408144</v>
@@ -2857,7 +2857,7 @@
         <v>2.595979058028602e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003566778386815546</v>
+        <v>0.0003566778386815545</v>
       </c>
       <c r="EH5" t="n">
         <v>0.000161701156740526</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5299345748921439</v>
+        <v>0.5299345748921442</v>
       </c>
       <c r="C6" t="n">
         <v>0.002052522295729635</v>
@@ -2899,13 +2899,13 @@
         <v>0.05311555413821412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2597610983239374</v>
+        <v>0.2597610983239371</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7354167727618743</v>
+        <v>0.7354167727618759</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2500945290249984</v>
+        <v>0.2500945290249986</v>
       </c>
       <c r="I6" t="n">
         <v>0.01882724461164284</v>
@@ -2917,28 +2917,28 @@
         <v>0.01487235815127472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07654208226067589</v>
+        <v>0.07654208226067591</v>
       </c>
       <c r="M6" t="n">
         <v>0.01897304135694425</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02722883903532964</v>
+        <v>0.02722883903532965</v>
       </c>
       <c r="O6" t="n">
         <v>0.003321018454892488</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01790940589409326</v>
+        <v>0.01790940589409325</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01776274626103379</v>
+        <v>0.004559561906338801</v>
       </c>
       <c r="R6" t="n">
         <v>0.01120296569583824</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009966703201301726</v>
+        <v>0.009966703201301724</v>
       </c>
       <c r="T6" t="n">
         <v>0.03304916023300448</v>
@@ -2947,7 +2947,7 @@
         <v>0.0001948919036789245</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002791749517589425</v>
+        <v>0.002791749517589424</v>
       </c>
       <c r="W6" t="n">
         <v>0.02041963799956447</v>
@@ -2956,10 +2956,10 @@
         <v>0.0003488135006925976</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004787929336587384</v>
+        <v>0.004787929336587385</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008182569425873226</v>
+        <v>0.008182569425873228</v>
       </c>
       <c r="AA6" t="n">
         <v>0.02704689096483576</v>
@@ -2968,7 +2968,7 @@
         <v>0.001971094732713696</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.09473253722403052</v>
+        <v>0.09473253722403055</v>
       </c>
       <c r="AD6" t="n">
         <v>0.0001012075968074319</v>
@@ -2977,13 +2977,13 @@
         <v>4.906307873887535e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0743377096514611</v>
+        <v>0.07433770965146112</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.03439410242006812</v>
+        <v>0.0343941024200681</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.004022204548822599</v>
+        <v>0.0040222045488226</v>
       </c>
       <c r="AI6" t="n">
         <v>0.001312010375700409</v>
@@ -2992,13 +2992,13 @@
         <v>0.004434309592505877</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03004678029158372</v>
+        <v>0.03004678029158371</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.00273702015401011</v>
+        <v>0.002737020154010111</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.000537921379969539</v>
+        <v>0.0005379213799695389</v>
       </c>
       <c r="AN6" t="n">
         <v>0.0003878002346536198</v>
@@ -3010,7 +3010,7 @@
         <v>0.001527998949199265</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.004137967556402722</v>
+        <v>0.00413796755640272</v>
       </c>
       <c r="AR6" t="n">
         <v>0.009459831609073932</v>
@@ -3028,25 +3028,25 @@
         <v>0.002948587112102971</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.03336475050455582</v>
+        <v>0.03336475050455581</v>
       </c>
       <c r="AX6" t="n">
         <v>0.002060400868615999</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.06683035884600767</v>
+        <v>0.06683035884600763</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.001044877016934704</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0004743458482385441</v>
+        <v>0.000474345848238544</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.05013015966437436</v>
+        <v>0.05013015966437438</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.01610452520371405</v>
+        <v>0.01610452520371406</v>
       </c>
       <c r="BD6" t="n">
         <v>0.02713723734740475</v>
@@ -3055,7 +3055,7 @@
         <v>0.002072790663001631</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.002257707073948502</v>
+        <v>0.002257707073948503</v>
       </c>
       <c r="BG6" t="n">
         <v>0.002817352188473341</v>
@@ -3064,7 +3064,7 @@
         <v>0.0155042431332785</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.000748435886857187</v>
+        <v>0.0007484358868571866</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.001197801319526733</v>
@@ -3076,31 +3076,31 @@
         <v>0.0002488192845270584</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0458663453672339</v>
+        <v>0.04586634536723391</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.00312322831189249</v>
+        <v>0.003123228311892491</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001611504078308822</v>
+        <v>0.0001611504078308821</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0007652754105711877</v>
+        <v>0.0007652754105711879</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0009224275781005866</v>
+        <v>0.0009224275781005867</v>
       </c>
       <c r="BR6" t="n">
         <v>0.001584042343902421</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.01798921758954268</v>
+        <v>0.01798921758954269</v>
       </c>
       <c r="BT6" t="n">
         <v>0.008108719038480856</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.008161945297350785</v>
+        <v>0.008161945297350783</v>
       </c>
       <c r="BV6" t="n">
         <v>0.005837382553381109</v>
@@ -3166,7 +3166,7 @@
         <v>0.001491023372163032</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00233539046969289</v>
+        <v>0.002335390469692889</v>
       </c>
       <c r="CR6" t="n">
         <v>0.0006871283703234461</v>
@@ -3175,16 +3175,16 @@
         <v>0.0002709033954802791</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0008836832052067202</v>
+        <v>0.0008836832052067201</v>
       </c>
       <c r="CU6" t="n">
         <v>0.0006115216132998973</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0008906213778691451</v>
+        <v>0.0008906213778691452</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0006960780778165507</v>
+        <v>0.0006960780778165506</v>
       </c>
       <c r="CX6" t="n">
         <v>0.005287649088268391</v>
@@ -3202,7 +3202,7 @@
         <v>0.00103786804023258</v>
       </c>
       <c r="DC6" t="n">
-        <v>9.23725588955633e-05</v>
+        <v>9.237255889556328e-05</v>
       </c>
       <c r="DD6" t="n">
         <v>0.003912659377694609</v>
@@ -3232,7 +3232,7 @@
         <v>0.0005140182423785839</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0006048326029876992</v>
+        <v>0.0006048326029876993</v>
       </c>
       <c r="DN6" t="n">
         <v>7.5078812667771e-05</v>
@@ -3241,7 +3241,7 @@
         <v>0.004275187196391888</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.1389432241631539</v>
+        <v>0.138943224163154</v>
       </c>
       <c r="DQ6" t="n">
         <v>5.525150980567452e-05</v>
@@ -3253,7 +3253,7 @@
         <v>0.002934382728566143</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.002702080112229179</v>
+        <v>0.00270208011222918</v>
       </c>
       <c r="DU6" t="n">
         <v>0.005250713318566989</v>
@@ -3268,16 +3268,16 @@
         <v>0.001647212024518754</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0003449532390662185</v>
+        <v>0.0003449532390662186</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0006921090278433128</v>
+        <v>0.0006921090278433129</v>
       </c>
       <c r="EA6" t="n">
         <v>0.0008494494444851188</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0007471502133908296</v>
+        <v>0.0007471502133908293</v>
       </c>
       <c r="EC6" t="n">
         <v>0.02245359767817744</v>
@@ -3286,7 +3286,7 @@
         <v>5.547178709305567e-05</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0002852076061572522</v>
+        <v>0.0002852076061572521</v>
       </c>
       <c r="EF6" t="n">
         <v>3.86500374251305e-05</v>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5498365034764119</v>
+        <v>0.5498365034764117</v>
       </c>
       <c r="C7" t="n">
         <v>0.002087270898910748</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002810496566621991</v>
+        <v>0.00281049656662199</v>
       </c>
       <c r="E7" t="n">
         <v>0.05844541456430546</v>
@@ -3337,10 +3337,10 @@
         <v>0.257973822620359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7438054494885259</v>
+        <v>0.7438054494885242</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2722809141344965</v>
+        <v>0.2722809141344964</v>
       </c>
       <c r="I7" t="n">
         <v>0.02145273836507618</v>
@@ -3349,25 +3349,25 @@
         <v>0.05106865028768307</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01642078699346755</v>
+        <v>0.01642078699346756</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07864084547411457</v>
+        <v>0.07864084547411464</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0188920781635471</v>
+        <v>0.01889207816354709</v>
       </c>
       <c r="N7" t="n">
         <v>0.02866800017020112</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003852164233230872</v>
+        <v>0.003852164233230871</v>
       </c>
       <c r="P7" t="n">
         <v>0.01793331838457235</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01803588093844935</v>
+        <v>0.004791354759121534</v>
       </c>
       <c r="R7" t="n">
         <v>0.01136827337291785</v>
@@ -3376,7 +3376,7 @@
         <v>0.0104555118061301</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03554256159213797</v>
+        <v>0.03554256159213796</v>
       </c>
       <c r="U7" t="n">
         <v>0.0002339038757284055</v>
@@ -3394,10 +3394,10 @@
         <v>0.005117893676660294</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008113054679726535</v>
+        <v>0.008113054679726532</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02988480033380324</v>
+        <v>0.02988480033380326</v>
       </c>
       <c r="AB7" t="n">
         <v>0.002114148642329313</v>
@@ -3409,7 +3409,7 @@
         <v>0.000101555640688846</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.228969246323985e-05</v>
+        <v>5.228969246323984e-05</v>
       </c>
       <c r="AF7" t="n">
         <v>0.07935642952320011</v>
@@ -3418,13 +3418,13 @@
         <v>0.03779816440700071</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.004320029478722486</v>
+        <v>0.004320029478722487</v>
       </c>
       <c r="AI7" t="n">
         <v>0.001433308977870862</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004689226111695493</v>
+        <v>0.004689226111695494</v>
       </c>
       <c r="AK7" t="n">
         <v>0.03167848379216123</v>
@@ -3433,22 +3433,22 @@
         <v>0.00277129154710259</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0005094361650311695</v>
+        <v>0.0005094361650311694</v>
       </c>
       <c r="AN7" t="n">
         <v>0.0004460484831528894</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.002153690227199782</v>
+        <v>0.002153690227199781</v>
       </c>
       <c r="AP7" t="n">
         <v>0.001597548719730897</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.004869451527405146</v>
+        <v>0.004869451527405145</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.009926880235855742</v>
+        <v>0.009926880235855744</v>
       </c>
       <c r="AS7" t="n">
         <v>9.168524798250091e-05</v>
@@ -3463,7 +3463,7 @@
         <v>0.00326873929005181</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03160813167020439</v>
+        <v>0.03160813167020438</v>
       </c>
       <c r="AX7" t="n">
         <v>0.002086870033959053</v>
@@ -3481,10 +3481,10 @@
         <v>0.05378662633875941</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.01828864524185311</v>
+        <v>0.0182886452418531</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02745495100305361</v>
+        <v>0.0274549510030536</v>
       </c>
       <c r="BE7" t="n">
         <v>0.002249426023151747</v>
@@ -3496,10 +3496,10 @@
         <v>0.002905578030942122</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.01510053891192217</v>
+        <v>0.01510053891192218</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0009234928852318332</v>
+        <v>0.0009234928852318333</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.001119160970588171</v>
@@ -3511,16 +3511,16 @@
         <v>0.00028267135169167</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04653094061048647</v>
+        <v>0.04653094061048648</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003266894744771807</v>
+        <v>0.003266894744771806</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001563517965014187</v>
+        <v>0.0001563517965014188</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0008057069611352638</v>
+        <v>0.0008057069611352637</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.001083743404042665</v>
@@ -3529,7 +3529,7 @@
         <v>0.001320333831176707</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01720138981481682</v>
+        <v>0.01720138981481681</v>
       </c>
       <c r="BT7" t="n">
         <v>0.009167781418569682</v>
@@ -3538,10 +3538,10 @@
         <v>0.00878557761602154</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.00637286854134105</v>
+        <v>0.006372868541341049</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.861100961586716e-05</v>
+        <v>5.861100961586715e-05</v>
       </c>
       <c r="BX7" t="n">
         <v>0.002796776490882463</v>
@@ -3559,19 +3559,19 @@
         <v>0.0006353970761973707</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0002646866427041027</v>
+        <v>0.0002646866427041028</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0006359991163367579</v>
+        <v>0.000635999116336758</v>
       </c>
       <c r="CE7" t="n">
         <v>0.01245843541731129</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001626783481283953</v>
+        <v>0.001626783481283952</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0141236333193693</v>
+        <v>0.01412363331936931</v>
       </c>
       <c r="CH7" t="n">
         <v>0.001380885892498201</v>
@@ -3610,13 +3610,13 @@
         <v>0.0002672970124425578</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.000889153670599746</v>
+        <v>0.0008891536705997459</v>
       </c>
       <c r="CU7" t="n">
         <v>0.0005796830832752918</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0009348816748506265</v>
+        <v>0.0009348816748506264</v>
       </c>
       <c r="CW7" t="n">
         <v>0.0007002550810807525</v>
@@ -3637,10 +3637,10 @@
         <v>0.0010940370274534</v>
       </c>
       <c r="DC7" t="n">
-        <v>8.21412341910832e-05</v>
+        <v>8.214123419108322e-05</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.003911389092343221</v>
+        <v>0.003911389092343222</v>
       </c>
       <c r="DE7" t="n">
         <v>0.0002754556854647917</v>
@@ -3658,13 +3658,13 @@
         <v>0.0001799903646665327</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0004435784266270909</v>
+        <v>0.0004435784266270908</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.003531578682380605</v>
+        <v>0.003531578682380606</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0005344276298555597</v>
+        <v>0.0005344276298555598</v>
       </c>
       <c r="DM7" t="n">
         <v>0.0008632836287606963</v>
@@ -3673,7 +3673,7 @@
         <v>7.481891910510263e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.004567702552234479</v>
+        <v>0.004567702552234477</v>
       </c>
       <c r="DP7" t="n">
         <v>0.1474095982813083</v>
@@ -3706,7 +3706,7 @@
         <v>0.0003620476414404139</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0007255594392149064</v>
+        <v>0.0007255594392149065</v>
       </c>
       <c r="EA7" t="n">
         <v>0.0008205405695680742</v>
@@ -3718,7 +3718,7 @@
         <v>0.02280775730296472</v>
       </c>
       <c r="ED7" t="n">
-        <v>5.430274172831246e-05</v>
+        <v>5.430274172831245e-05</v>
       </c>
       <c r="EE7" t="n">
         <v>0.0002901622116690434</v>
@@ -3727,7 +3727,7 @@
         <v>3.495848599844757e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0004733129871558358</v>
+        <v>0.0004733129871558357</v>
       </c>
       <c r="EH7" t="n">
         <v>0.0002153518739168433</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3224824066495271</v>
+        <v>0.3224824066495273</v>
       </c>
       <c r="C8" t="n">
         <v>0.001242197792708662</v>
@@ -3769,10 +3769,10 @@
         <v>0.03776290364606211</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1521324908624406</v>
+        <v>0.1521324908624405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4470358992766115</v>
+        <v>0.447035899276611</v>
       </c>
       <c r="H8" t="n">
         <v>0.1623253700870058</v>
@@ -3784,10 +3784,10 @@
         <v>0.02937213074997121</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009399903997977578</v>
+        <v>0.009399903997977577</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04669290578964692</v>
+        <v>0.04669290578964694</v>
       </c>
       <c r="M8" t="n">
         <v>0.01157946910150908</v>
@@ -3802,16 +3802,16 @@
         <v>0.01105384267654917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01118877651293113</v>
+        <v>0.002786718522644208</v>
       </c>
       <c r="R8" t="n">
-        <v>0.006459455786842915</v>
+        <v>0.006459455786842917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00603883317786996</v>
+        <v>0.006038833177869958</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01894994676672051</v>
+        <v>0.01894994676672049</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001407989612484488</v>
@@ -3832,7 +3832,7 @@
         <v>0.004638300344483265</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01764582845156707</v>
+        <v>0.01764582845156708</v>
       </c>
       <c r="AB8" t="n">
         <v>0.001239633943453578</v>
@@ -3841,22 +3841,22 @@
         <v>0.05368801768315602</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.867675502352838e-05</v>
+        <v>5.867675502352839e-05</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.098094687305593e-05</v>
+        <v>3.098094687305592e-05</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.04537530795707354</v>
+        <v>0.04537530795707351</v>
       </c>
       <c r="AG8" t="n">
         <v>0.02287967814750632</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002572561284717415</v>
+        <v>0.002572561284717413</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0009249441436916951</v>
+        <v>0.0009249441436916952</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.002648230627924265</v>
@@ -3877,19 +3877,19 @@
         <v>0.001275424127968762</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0009659948871630073</v>
+        <v>0.0009659948871630072</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002722844943801618</v>
+        <v>0.002722844943801619</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.005812349104038782</v>
+        <v>0.005812349104038784</v>
       </c>
       <c r="AS8" t="n">
         <v>5.547814050348534e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0002792472210710254</v>
+        <v>0.0002792472210710255</v>
       </c>
       <c r="AU8" t="n">
         <v>0.000349031745384101</v>
@@ -3898,19 +3898,19 @@
         <v>0.002055560499385458</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.01994039272251266</v>
+        <v>0.01994039272251267</v>
       </c>
       <c r="AX8" t="n">
         <v>0.001166917358139959</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.03764280843651709</v>
+        <v>0.03764280843651707</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0007596783446968599</v>
+        <v>0.0007596783446968597</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0002679094589926524</v>
+        <v>0.0002679094589926523</v>
       </c>
       <c r="BB8" t="n">
         <v>0.0335717155862528</v>
@@ -3931,16 +3931,16 @@
         <v>0.001646469345053551</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.009564491336446284</v>
+        <v>0.009564491336446287</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0005922169561856191</v>
+        <v>0.000592216956185619</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0005733084128010694</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.008710621474147289</v>
+        <v>0.008710621474147293</v>
       </c>
       <c r="BL8" t="n">
         <v>0.0001616149611932084</v>
@@ -3967,7 +3967,7 @@
         <v>0.01104964306908993</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.004668600432800849</v>
+        <v>0.00466860043280085</v>
       </c>
       <c r="BU8" t="n">
         <v>0.005038264794166815</v>
@@ -3988,7 +3988,7 @@
         <v>0.02673056287782778</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002294778551166659</v>
+        <v>0.0002294778551166658</v>
       </c>
       <c r="CB8" t="n">
         <v>0.0004049105400889481</v>
@@ -4006,10 +4006,10 @@
         <v>0.001021395072856708</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.00884346664819266</v>
+        <v>0.008843466648192659</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.000886652461350247</v>
+        <v>0.0008866524613502471</v>
       </c>
       <c r="CI8" t="n">
         <v>0.0001601249081986631</v>
@@ -4024,7 +4024,7 @@
         <v>0.001342569985988429</v>
       </c>
       <c r="CM8" t="n">
-        <v>4.975013327154167e-05</v>
+        <v>4.975013327154168e-05</v>
       </c>
       <c r="CN8" t="n">
         <v>0.0003610304352502873</v>
@@ -4051,7 +4051,7 @@
         <v>0.0002663731876371467</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0005869454417393584</v>
+        <v>0.0005869454417393583</v>
       </c>
       <c r="CW8" t="n">
         <v>0.0003804793552433966</v>
@@ -4060,7 +4060,7 @@
         <v>0.003877977339002642</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0001931943136576656</v>
+        <v>0.0001931943136576657</v>
       </c>
       <c r="CZ8" t="n">
         <v>0.0004451847009890992</v>
@@ -4072,7 +4072,7 @@
         <v>0.0007057263057469818</v>
       </c>
       <c r="DC8" t="n">
-        <v>5.623814756304433e-05</v>
+        <v>5.623814756304434e-05</v>
       </c>
       <c r="DD8" t="n">
         <v>0.002493301695519587</v>
@@ -4084,7 +4084,7 @@
         <v>0.001534226153400127</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.007695683884927151</v>
+        <v>0.00769568388492715</v>
       </c>
       <c r="DH8" t="n">
         <v>0.001417531074534073</v>
@@ -4111,22 +4111,22 @@
         <v>0.002282621296694471</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.08403632211407105</v>
+        <v>0.08403632211407107</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.808987432740123e-05</v>
+        <v>2.808987432740122e-05</v>
       </c>
       <c r="DR8" t="n">
         <v>0.0001085845380413202</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001753971152354447</v>
+        <v>0.001753971152354448</v>
       </c>
       <c r="DT8" t="n">
         <v>0.001370349897257407</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.002957778103543683</v>
+        <v>0.002957778103543684</v>
       </c>
       <c r="DV8" t="n">
         <v>0.0006529475512652217</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3436030939561708</v>
+        <v>0.3436030939561711</v>
       </c>
       <c r="C9" t="n">
         <v>0.001357810167937169</v>
@@ -4207,7 +4207,7 @@
         <v>0.1713058781983859</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4572292602392651</v>
+        <v>0.4572292602392647</v>
       </c>
       <c r="H9" t="n">
         <v>0.1812455655763622</v>
@@ -4222,28 +4222,28 @@
         <v>0.01234036595382299</v>
       </c>
       <c r="L9" t="n">
-        <v>0.049425513232121</v>
+        <v>0.04942551323212097</v>
       </c>
       <c r="M9" t="n">
         <v>0.01186969215487272</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01919433906531263</v>
+        <v>0.01919433906531262</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002603928469516504</v>
+        <v>0.002603928469516502</v>
       </c>
       <c r="P9" t="n">
         <v>0.01100274219344514</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01169316090710923</v>
+        <v>0.002935211022822908</v>
       </c>
       <c r="R9" t="n">
-        <v>0.007074824289377801</v>
+        <v>0.007074824289377802</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006743842536240281</v>
+        <v>0.006743842536240283</v>
       </c>
       <c r="T9" t="n">
         <v>0.02110677083946469</v>
@@ -4264,7 +4264,7 @@
         <v>0.003263107281701314</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004785109183876044</v>
+        <v>0.004785109183876045</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01641213128614903</v>
@@ -4273,7 +4273,7 @@
         <v>0.001262290025432175</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05589105076963588</v>
+        <v>0.05589105076963585</v>
       </c>
       <c r="AD9" t="n">
         <v>5.897603557607187e-05</v>
@@ -4282,22 +4282,22 @@
         <v>2.922848646382211e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04542680898001225</v>
+        <v>0.04542680898001226</v>
       </c>
       <c r="AG9" t="n">
         <v>0.03127020992059677</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002819562939157048</v>
+        <v>0.002819562939157047</v>
       </c>
       <c r="AI9" t="n">
         <v>0.001045215912405165</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002723558143193918</v>
+        <v>0.002723558143193919</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01832972921972574</v>
+        <v>0.01832972921972575</v>
       </c>
       <c r="AL9" t="n">
         <v>0.001624610963324564</v>
@@ -4309,7 +4309,7 @@
         <v>0.0002964771009169858</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001485119277915443</v>
+        <v>0.001485119277915442</v>
       </c>
       <c r="AP9" t="n">
         <v>0.001107415822511123</v>
@@ -4318,7 +4318,7 @@
         <v>0.003542963793128389</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.005969006125607705</v>
+        <v>0.005969006125607702</v>
       </c>
       <c r="AS9" t="n">
         <v>5.82519324332952e-05</v>
@@ -4336,19 +4336,19 @@
         <v>0.01777785125531894</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001141280828365574</v>
+        <v>0.001141280828365575</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03423900230091092</v>
+        <v>0.03423900230091094</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.0007230429567978425</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0002699688905173945</v>
+        <v>0.0002699688905173946</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.038554184362628</v>
+        <v>0.03855418436262799</v>
       </c>
       <c r="BC9" t="n">
         <v>0.01276953653545165</v>
@@ -4363,19 +4363,19 @@
         <v>0.001629159765240906</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.001711209829760502</v>
+        <v>0.001711209829760501</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.009733931060641243</v>
+        <v>0.009733931060641242</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006712524231893295</v>
+        <v>0.0006712524231893297</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0005640805295265376</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.009985327648659397</v>
+        <v>0.009985327648659396</v>
       </c>
       <c r="BL9" t="n">
         <v>0.0002121567561215569</v>
@@ -4402,13 +4402,13 @@
         <v>0.01241404671556724</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005076106647535061</v>
+        <v>0.005076106647535062</v>
       </c>
       <c r="BU9" t="n">
         <v>0.005625032049677993</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.004463965983382725</v>
+        <v>0.004463965983382726</v>
       </c>
       <c r="BW9" t="n">
         <v>4.13275609000788e-05</v>
@@ -4417,7 +4417,7 @@
         <v>0.001684052978021976</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0005155437991174841</v>
+        <v>0.0005155437991174842</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.02731338190409919</v>
@@ -4441,7 +4441,7 @@
         <v>0.001136787605346194</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009207433104408644</v>
+        <v>0.009207433104408648</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0008629487862571331</v>
@@ -4471,7 +4471,7 @@
         <v>0.0007701658318890083</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001301623680192521</v>
+        <v>0.00130162368019252</v>
       </c>
       <c r="CR9" t="n">
         <v>0.0004695385815555212</v>
@@ -4498,7 +4498,7 @@
         <v>0.0001943882112391087</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.000471234315894353</v>
+        <v>0.0004712343158943529</v>
       </c>
       <c r="DA9" t="n">
         <v>0.0009963581622997369</v>
@@ -4531,13 +4531,13 @@
         <v>0.0002597164623331289</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002121825096900875</v>
+        <v>0.002121825096900876</v>
       </c>
       <c r="DL9" t="n">
         <v>0.0003765164153026662</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0008457204364124961</v>
+        <v>0.0008457204364124963</v>
       </c>
       <c r="DN9" t="n">
         <v>4.523423653003045e-05</v>
@@ -4546,7 +4546,7 @@
         <v>0.002309389974654582</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.07630067143219156</v>
+        <v>0.07630067143219157</v>
       </c>
       <c r="DQ9" t="n">
         <v>2.940536967602855e-05</v>
@@ -4576,7 +4576,7 @@
         <v>0.0002153248561332576</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004156891397307701</v>
+        <v>0.0004156891397307702</v>
       </c>
       <c r="EA9" t="n">
         <v>0.0004701242750660571</v>

--- a/data/proteomics/organell_protein_volume_tao2.xlsx
+++ b/data/proteomics/organell_protein_volume_tao2.xlsx
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7206766012475397</v>
+        <v>0.7206766012475402</v>
       </c>
       <c r="C2" t="n">
         <v>0.002165212380823581</v>
@@ -1159,16 +1159,16 @@
         <v>0.0534906314377176</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2759418730875773</v>
+        <v>0.2759418730875776</v>
       </c>
       <c r="G2" t="n">
         <v>1.026677773232596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2933550807927053</v>
+        <v>0.2933550807927051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01878197683417896</v>
+        <v>0.01878197683417897</v>
       </c>
       <c r="J2" t="n">
         <v>0.03689411485103833</v>
@@ -1177,22 +1177,22 @@
         <v>0.01417496949717756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07504183978345613</v>
+        <v>0.07504183978345619</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007410358115722399</v>
+        <v>0.0074103581157224</v>
       </c>
       <c r="N2" t="n">
-        <v>0.03172569423987596</v>
+        <v>0.03172569423987595</v>
       </c>
       <c r="O2" t="n">
         <v>0.006198464546696099</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01641634096772068</v>
+        <v>0.01641634096772069</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.004967979449627478</v>
+        <v>0.004967979449627477</v>
       </c>
       <c r="R2" t="n">
         <v>0.0113377798648723</v>
@@ -1201,16 +1201,16 @@
         <v>0.01041929992239056</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03206229630425289</v>
+        <v>0.0320622963042529</v>
       </c>
       <c r="U2" t="n">
         <v>0.000145053531129478</v>
       </c>
       <c r="V2" t="n">
-        <v>0.002668762731131356</v>
+        <v>0.002668762731131357</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02718682175248843</v>
+        <v>0.02718682175248842</v>
       </c>
       <c r="X2" t="n">
         <v>0.0003656975943547267</v>
@@ -1219,10 +1219,10 @@
         <v>0.005314854279585013</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0085848992198461</v>
+        <v>0.008584899219846101</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03892445205620821</v>
+        <v>0.03892445205620823</v>
       </c>
       <c r="AB2" t="n">
         <v>0.002104212287918602</v>
@@ -1234,22 +1234,22 @@
         <v>0.000120357173627712</v>
       </c>
       <c r="AE2" t="n">
-        <v>5.507364114259175e-05</v>
+        <v>5.507364114259176e-05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08874967499681236</v>
+        <v>0.08874967499681238</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.03486329942636325</v>
+        <v>0.03486329942636326</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.0047757036654749</v>
+        <v>0.004775703665474898</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001385770745017591</v>
+        <v>0.00138577074501759</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.004825647692773463</v>
+        <v>0.004825647692773465</v>
       </c>
       <c r="AK2" t="n">
         <v>0.03385765157792101</v>
@@ -1264,13 +1264,13 @@
         <v>0.0003594892964050996</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.001985371456696078</v>
+        <v>0.001985371456696077</v>
       </c>
       <c r="AP2" t="n">
         <v>0.001504528918223736</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.004687852375112363</v>
+        <v>0.004687852375112362</v>
       </c>
       <c r="AR2" t="n">
         <v>0.01039381494161817</v>
@@ -1279,7 +1279,7 @@
         <v>8.071701180739867e-05</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0004233345722119058</v>
+        <v>0.000423334572211906</v>
       </c>
       <c r="AU2" t="n">
         <v>0.0005314101706905116</v>
@@ -1294,28 +1294,28 @@
         <v>0.003408458254454325</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.09772824350641907</v>
+        <v>0.09772824350641911</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0009845292239379121</v>
+        <v>0.0009845292239379119</v>
       </c>
       <c r="BA2" t="n">
         <v>0.000506041218920848</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05058979606964792</v>
+        <v>0.05058979606964794</v>
       </c>
       <c r="BC2" t="n">
         <v>0.01692564880503614</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.03098459650943752</v>
+        <v>0.03098459650943751</v>
       </c>
       <c r="BE2" t="n">
         <v>0.002276368382593859</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.002411484928312958</v>
+        <v>0.002411484928312956</v>
       </c>
       <c r="BG2" t="n">
         <v>0.003472351442984559</v>
@@ -1324,13 +1324,13 @@
         <v>0.01249855510780769</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0006521834794809147</v>
+        <v>0.0006521834794809148</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.001917763204470912</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.01427705614429741</v>
+        <v>0.01427705614429742</v>
       </c>
       <c r="BL2" t="n">
         <v>0.0002648996720415359</v>
@@ -1339,16 +1339,16 @@
         <v>0.1153208705295821</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.003548870991374987</v>
+        <v>0.003548870991374988</v>
       </c>
       <c r="BO2" t="n">
         <v>0.0001397935434013381</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.000715254836737915</v>
+        <v>0.0007152548367379151</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0009558292781177678</v>
+        <v>0.0009558292781177676</v>
       </c>
       <c r="BR2" t="n">
         <v>0.001645885209264682</v>
@@ -1366,13 +1366,13 @@
         <v>0.006038919711564021</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7077263537551e-05</v>
+        <v>5.707726353755101e-05</v>
       </c>
       <c r="BX2" t="n">
         <v>0.003008266286336013</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0008972888070224709</v>
+        <v>0.000897288807022471</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.0009400126599844494</v>
@@ -1387,13 +1387,13 @@
         <v>0.0003458744746313962</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0007543857748958557</v>
+        <v>0.0007543857748958558</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.005894623447802896</v>
+        <v>0.005894623447802895</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.000954774383751366</v>
+        <v>0.0009547743837513662</v>
       </c>
       <c r="CG2" t="n">
         <v>0.002687752657255408</v>
@@ -1402,7 +1402,7 @@
         <v>0.00120079789391442</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.0001978108277265193</v>
+        <v>0.0001978108277265192</v>
       </c>
       <c r="CJ2" t="n">
         <v>0.004753144560416166</v>
@@ -1423,13 +1423,13 @@
         <v>0.001558142153535212</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.003222230550180869</v>
+        <v>0.00322223055018087</v>
       </c>
       <c r="CQ2" t="n">
         <v>0.004407527250484313</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.000945433488637394</v>
+        <v>0.0009454334886373941</v>
       </c>
       <c r="CS2" t="n">
         <v>0.0003819449009389856</v>
@@ -1459,10 +1459,10 @@
         <v>0.0008479698973287356</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0009516361400175822</v>
+        <v>0.0009516361400175823</v>
       </c>
       <c r="DC2" t="n">
-        <v>9.690740714235118e-05</v>
+        <v>9.690740714235119e-05</v>
       </c>
       <c r="DD2" t="n">
         <v>0.004458160794493586</v>
@@ -1498,13 +1498,13 @@
         <v>9.506134334105387e-05</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.004675262105543023</v>
+        <v>0.004675262105543024</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.2018002370698954</v>
+        <v>0.2018002370698955</v>
       </c>
       <c r="DQ2" t="n">
-        <v>8.510981947950737e-05</v>
+        <v>8.510981947950738e-05</v>
       </c>
       <c r="DR2" t="n">
         <v>0.0002027411895147917</v>
@@ -1516,7 +1516,7 @@
         <v>0.003270992941904004</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.005166661664915852</v>
+        <v>0.005166661664915853</v>
       </c>
       <c r="DV2" t="n">
         <v>0.001522380293753885</v>
@@ -1531,13 +1531,13 @@
         <v>0.0004115641595516574</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.0009297940886889617</v>
+        <v>0.0009297940886889616</v>
       </c>
       <c r="EA2" t="n">
         <v>0.001284530472416466</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.0008440254103115965</v>
+        <v>0.0008440254103115964</v>
       </c>
       <c r="EC2" t="n">
         <v>0.02641732976563713</v>
@@ -1555,7 +1555,7 @@
         <v>0.0003625388352469172</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0001913265550433594</v>
+        <v>0.0001913265550433595</v>
       </c>
       <c r="EI2" t="n">
         <v>0.0001034215755709822</v>
@@ -1582,13 +1582,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7486753180912479</v>
+        <v>0.7486753180912474</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00259786534345715</v>
+        <v>0.002597865343457151</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003202166869715695</v>
+        <v>0.003202166869715696</v>
       </c>
       <c r="E3" t="n">
         <v>0.06076809088901151</v>
@@ -1600,10 +1600,10 @@
         <v>1.027783529499927</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3332922100880313</v>
+        <v>0.3332922100880315</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02504158188918005</v>
+        <v>0.02504158188918004</v>
       </c>
       <c r="J3" t="n">
         <v>0.0387051002436261</v>
@@ -1612,7 +1612,7 @@
         <v>0.01791084159389123</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08137628231289801</v>
+        <v>0.08137628231289802</v>
       </c>
       <c r="M3" t="n">
         <v>0.007628478768137784</v>
@@ -1621,13 +1621,13 @@
         <v>0.03506363152408568</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006951105782700873</v>
+        <v>0.006951105782700874</v>
       </c>
       <c r="P3" t="n">
         <v>0.01854546805473342</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005839857338368132</v>
+        <v>0.005839857338368127</v>
       </c>
       <c r="R3" t="n">
         <v>0.01312849779840527</v>
@@ -1645,7 +1645,7 @@
         <v>0.002875072698842628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.02845654439413756</v>
+        <v>0.02845654439413755</v>
       </c>
       <c r="X3" t="n">
         <v>0.0004125956048767483</v>
@@ -1654,31 +1654,31 @@
         <v>0.006021808482208379</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009614938255542715</v>
+        <v>0.009614938255542719</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03996716207904129</v>
+        <v>0.03996716207904127</v>
       </c>
       <c r="AB3" t="n">
         <v>0.00237217221774785</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.06009954207393826</v>
+        <v>0.06009954207393827</v>
       </c>
       <c r="AD3" t="n">
         <v>0.0001317697807861838</v>
       </c>
       <c r="AE3" t="n">
-        <v>5.774399582133145e-05</v>
+        <v>5.774399582133144e-05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.09767290382095491</v>
+        <v>0.09767290382095487</v>
       </c>
       <c r="AG3" t="n">
         <v>0.03539739824581133</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.005216149023496734</v>
+        <v>0.005216149023496735</v>
       </c>
       <c r="AI3" t="n">
         <v>0.001439201850859847</v>
@@ -1687,7 +1687,7 @@
         <v>0.005496880009575862</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03819211174009295</v>
+        <v>0.03819211174009297</v>
       </c>
       <c r="AL3" t="n">
         <v>0.003624242152922135</v>
@@ -1699,13 +1699,13 @@
         <v>0.0004522633937595655</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.00229039272601887</v>
+        <v>0.002290392726018871</v>
       </c>
       <c r="AP3" t="n">
         <v>0.001786713449581035</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.005212383520650791</v>
+        <v>0.00521238352065079</v>
       </c>
       <c r="AR3" t="n">
         <v>0.01121885551981897</v>
@@ -1738,13 +1738,13 @@
         <v>0.0005714311666559039</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0523088956848966</v>
+        <v>0.05230889568489658</v>
       </c>
       <c r="BC3" t="n">
         <v>0.01966568678614985</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.03586324812332643</v>
+        <v>0.03586324812332642</v>
       </c>
       <c r="BE3" t="n">
         <v>0.002663899499940106</v>
@@ -1753,7 +1753,7 @@
         <v>0.00276292907262157</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.003732412503245876</v>
+        <v>0.003732412503245875</v>
       </c>
       <c r="BH3" t="n">
         <v>0.01228235136643472</v>
@@ -1765,13 +1765,13 @@
         <v>0.001822310239093187</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01530153396880906</v>
+        <v>0.01530153396880905</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0002767092505913733</v>
+        <v>0.0002767092505913732</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1060120426921342</v>
+        <v>0.1060120426921343</v>
       </c>
       <c r="BN3" t="n">
         <v>0.003909902473840128</v>
@@ -1798,13 +1798,13 @@
         <v>0.01135150157225728</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.006928577250794115</v>
+        <v>0.006928577250794114</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.704664523449581e-05</v>
+        <v>6.704664523449579e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.003326500246901522</v>
+        <v>0.003326500246901521</v>
       </c>
       <c r="BY3" t="n">
         <v>0.001016974699588744</v>
@@ -1813,7 +1813,7 @@
         <v>0.001504333596607258</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0005039652044605499</v>
+        <v>0.0005039652044605498</v>
       </c>
       <c r="CB3" t="n">
         <v>0.0006297246876554948</v>
@@ -1828,13 +1828,13 @@
         <v>0.006895022817362434</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0009991731096861052</v>
+        <v>0.0009991731096861054</v>
       </c>
       <c r="CG3" t="n">
         <v>0.002862344728263664</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.001370304183280832</v>
+        <v>0.001370304183280833</v>
       </c>
       <c r="CI3" t="n">
         <v>0.000356329161487872</v>
@@ -1852,16 +1852,16 @@
         <v>0.000178088608768983</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0006850561851480443</v>
+        <v>0.0006850561851480445</v>
       </c>
       <c r="CO3" t="n">
         <v>0.001211187058158237</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.003639869019038072</v>
+        <v>0.003639869019038071</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.004769436485694281</v>
+        <v>0.004769436485694282</v>
       </c>
       <c r="CR3" t="n">
         <v>0.0009321793608618741</v>
@@ -1879,7 +1879,7 @@
         <v>0.001073794422543585</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0008624287186771865</v>
+        <v>0.0008624287186771866</v>
       </c>
       <c r="CX3" t="n">
         <v>0.007174601744675881</v>
@@ -1888,7 +1888,7 @@
         <v>0.000470425138479064</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.000945147244984271</v>
+        <v>0.0009451472449842712</v>
       </c>
       <c r="DA3" t="n">
         <v>0.001090625075925172</v>
@@ -1900,7 +1900,7 @@
         <v>0.0001022315132066139</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.004527948733535526</v>
+        <v>0.004527948733535525</v>
       </c>
       <c r="DE3" t="n">
         <v>0.0003528890617523331</v>
@@ -1915,7 +1915,7 @@
         <v>0.002552290847724183</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0002212899388323334</v>
+        <v>0.0002212899388323335</v>
       </c>
       <c r="DJ3" t="n">
         <v>0.0004558950666888724</v>
@@ -1936,7 +1936,7 @@
         <v>0.005199894661483803</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.1954248287620582</v>
+        <v>0.1954248287620581</v>
       </c>
       <c r="DQ3" t="n">
         <v>9.24848858154068e-05</v>
@@ -1951,7 +1951,7 @@
         <v>0.003173557723967845</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.006102903919862789</v>
+        <v>0.006102903919862788</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0016305727947586</v>
@@ -1963,13 +1963,13 @@
         <v>0.002157031193510175</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0004277224429845476</v>
+        <v>0.0004277224429845475</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.001064057079870106</v>
+        <v>0.001064057079870107</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.001197708058567181</v>
+        <v>0.001197708058567182</v>
       </c>
       <c r="EB3" t="n">
         <v>0.000958419526520414</v>
@@ -2017,40 +2017,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3430553657108142</v>
+        <v>0.3430553657108149</v>
       </c>
       <c r="C4" t="n">
         <v>0.000885670438494863</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001418496529634649</v>
+        <v>0.00141849652963465</v>
       </c>
       <c r="E4" t="n">
         <v>0.03823944859638725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1675448549038018</v>
+        <v>0.1675448549038021</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5177130940050545</v>
+        <v>0.5177130940050539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1803172662575532</v>
+        <v>0.1803172662575531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01326588465130503</v>
+        <v>0.01326588465130502</v>
       </c>
       <c r="J4" t="n">
         <v>0.02704253700713397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007755983548600881</v>
+        <v>0.007755983548600882</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04148637488097948</v>
+        <v>0.04148637488097952</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009848290384017975</v>
+        <v>0.009848290384017978</v>
       </c>
       <c r="N4" t="n">
         <v>0.02020569778623052</v>
@@ -2059,19 +2059,19 @@
         <v>0.002961602000507267</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01000549589439204</v>
+        <v>0.01000549589439205</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.002388290622986099</v>
+        <v>0.0023882906229861</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005301905166709754</v>
+        <v>0.005301905166709758</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005679545102279857</v>
+        <v>0.005679545102279854</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01592194300676973</v>
+        <v>0.01592194300676974</v>
       </c>
       <c r="U4" t="n">
         <v>9.757264860685046e-05</v>
@@ -2083,7 +2083,7 @@
         <v>0.01464827675648381</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0001326931324769748</v>
+        <v>0.0001326931324769749</v>
       </c>
       <c r="Y4" t="n">
         <v>0.003620375266243745</v>
@@ -2092,16 +2092,16 @@
         <v>0.003599326927027622</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02252219665124339</v>
+        <v>0.02252219665124338</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0009652623038228178</v>
+        <v>0.0009652623038228175</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.04394894672626477</v>
+        <v>0.04394894672626475</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.775459849322818e-05</v>
+        <v>5.775459849322819e-05</v>
       </c>
       <c r="AE4" t="n">
         <v>3.527440812506447e-05</v>
@@ -2119,7 +2119,7 @@
         <v>0.001176488845484316</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.002241453029249023</v>
+        <v>0.002241453029249024</v>
       </c>
       <c r="AK4" t="n">
         <v>0.01883392801411436</v>
@@ -2143,7 +2143,7 @@
         <v>0.003981141013338681</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00566803063459957</v>
+        <v>0.005668030634599569</v>
       </c>
       <c r="AS4" t="n">
         <v>5.398288266629993e-05</v>
@@ -2155,25 +2155,25 @@
         <v>0.000307490251926655</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.002030354463019791</v>
+        <v>0.00203035446301979</v>
       </c>
       <c r="AW4" t="n">
         <v>0.03262201908569498</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00122940016259373</v>
+        <v>0.001229400162593731</v>
       </c>
       <c r="AY4" t="n">
         <v>0.04532951408041016</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0007532864408251531</v>
+        <v>0.000753286440825153</v>
       </c>
       <c r="BA4" t="n">
         <v>0.0002464561791329419</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03478727565652049</v>
+        <v>0.03478727565652048</v>
       </c>
       <c r="BC4" t="n">
         <v>0.01263737092296079</v>
@@ -2191,19 +2191,19 @@
         <v>0.001719073327460638</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.01128448990784614</v>
+        <v>0.01128448990784615</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0005106781816962907</v>
+        <v>0.0005106781816962905</v>
       </c>
       <c r="BJ4" t="n">
         <v>0.0007646601323309712</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.00852028489917315</v>
+        <v>0.008520284899173152</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0002145544103420148</v>
+        <v>0.0002145544103420147</v>
       </c>
       <c r="BM4" t="n">
         <v>0.0314676960296232</v>
@@ -2221,19 +2221,19 @@
         <v>0.0007993134266321578</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0007198732219163446</v>
+        <v>0.0007198732219163445</v>
       </c>
       <c r="BS4" t="n">
         <v>0.01631326078087873</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.004608654807769026</v>
+        <v>0.004608654807769027</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005097165407296868</v>
+        <v>0.00509716540729687</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004514360845371798</v>
+        <v>0.004514360845371799</v>
       </c>
       <c r="BW4" t="n">
         <v>1.782815594159935e-05</v>
@@ -2266,7 +2266,7 @@
         <v>0.001268940738589457</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.007423196093336201</v>
+        <v>0.0074231960933362</v>
       </c>
       <c r="CH4" t="n">
         <v>0.0008008417200567042</v>
@@ -2305,7 +2305,7 @@
         <v>0.0001321732813335232</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0005327976803238158</v>
+        <v>0.0005327976803238159</v>
       </c>
       <c r="CU4" t="n">
         <v>0.0003570838860867273</v>
@@ -2335,7 +2335,7 @@
         <v>8.429344223720198e-05</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.003227950362975373</v>
+        <v>0.003227950362975371</v>
       </c>
       <c r="DE4" t="n">
         <v>0.0001203861095603063</v>
@@ -2344,13 +2344,13 @@
         <v>0.001579862571923998</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.008814575405249407</v>
+        <v>0.008814575405249409</v>
       </c>
       <c r="DH4" t="n">
         <v>0.00132538947282932</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0001503245223312976</v>
+        <v>0.0001503245223312975</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.0002435989733140792</v>
@@ -2365,7 +2365,7 @@
         <v>0.0005035210007240594</v>
       </c>
       <c r="DN4" t="n">
-        <v>5.40724381267699e-05</v>
+        <v>5.407243812676992e-05</v>
       </c>
       <c r="DO4" t="n">
         <v>0.002463368877445402</v>
@@ -2386,13 +2386,13 @@
         <v>0.0009571892435833397</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0021111026128303</v>
+        <v>0.002111102612830301</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0005294244760161973</v>
+        <v>0.0005294244760161971</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0008761793978261822</v>
+        <v>0.0008761793978261823</v>
       </c>
       <c r="DX4" t="n">
         <v>0.0008286565291732521</v>
@@ -2401,19 +2401,19 @@
         <v>0.0002445551906570032</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0003456426315875525</v>
+        <v>0.0003456426315875526</v>
       </c>
       <c r="EA4" t="n">
         <v>0.000648762239440483</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0004162119096121748</v>
+        <v>0.0004162119096121747</v>
       </c>
       <c r="EC4" t="n">
         <v>0.008208996067224092</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.000990017066224e-05</v>
+        <v>5.000990017066223e-05</v>
       </c>
       <c r="EE4" t="n">
         <v>0.0001273803772792078</v>
@@ -2425,10 +2425,10 @@
         <v>0.000235351232176808</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.871733344609494e-05</v>
+        <v>8.871733344609491e-05</v>
       </c>
       <c r="EI4" t="n">
-        <v>6.472961012042393e-05</v>
+        <v>6.472961012042392e-05</v>
       </c>
       <c r="EJ4" t="n">
         <v>3.582489021813718e-05</v>
@@ -2467,13 +2467,13 @@
         <v>0.2067008651660895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5610231483973882</v>
+        <v>0.5610231483973879</v>
       </c>
       <c r="H5" t="n">
         <v>0.2168575862518479</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01809708790491719</v>
+        <v>0.01809708790491718</v>
       </c>
       <c r="J5" t="n">
         <v>0.03948225734603457</v>
@@ -2482,7 +2482,7 @@
         <v>0.01397022867435818</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06133125873541262</v>
+        <v>0.06133125873541267</v>
       </c>
       <c r="M5" t="n">
         <v>0.01536358712727088</v>
@@ -2497,7 +2497,7 @@
         <v>0.01460750202411441</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.003636754291032936</v>
+        <v>0.003636754291032937</v>
       </c>
       <c r="R5" t="n">
         <v>0.008551162770785038</v>
@@ -2506,7 +2506,7 @@
         <v>0.008308315600061919</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02661502244646362</v>
+        <v>0.02661502244646363</v>
       </c>
       <c r="U5" t="n">
         <v>0.0001831603106425639</v>
@@ -2515,10 +2515,10 @@
         <v>0.002174382452263955</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01689654526829179</v>
+        <v>0.0168965452682918</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0002630559794953423</v>
+        <v>0.0002630559794953422</v>
       </c>
       <c r="Y5" t="n">
         <v>0.003920830544407507</v>
@@ -2527,25 +2527,25 @@
         <v>0.005801334335250112</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.02146323283558258</v>
+        <v>0.02146323283558257</v>
       </c>
       <c r="AB5" t="n">
         <v>0.001585090649620057</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.06886937735103742</v>
+        <v>0.06886937735103744</v>
       </c>
       <c r="AD5" t="n">
-        <v>7.441716504666132e-05</v>
+        <v>7.441716504666133e-05</v>
       </c>
       <c r="AE5" t="n">
         <v>3.856991155758002e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.05681907896462441</v>
+        <v>0.05681907896462445</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.03336788588497682</v>
+        <v>0.03336788588497681</v>
       </c>
       <c r="AH5" t="n">
         <v>0.003439969001883047</v>
@@ -2554,10 +2554,10 @@
         <v>0.001277485236306388</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.003436072503649582</v>
+        <v>0.003436072503649581</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.01978786011237625</v>
+        <v>0.01978786011237624</v>
       </c>
       <c r="AL5" t="n">
         <v>0.002074886524754874</v>
@@ -2575,7 +2575,7 @@
         <v>0.001418087622907469</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.004223869516288714</v>
+        <v>0.004223869516288712</v>
       </c>
       <c r="AR5" t="n">
         <v>0.007457918265478389</v>
@@ -2584,7 +2584,7 @@
         <v>7.149656626823477e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0004076070836833261</v>
+        <v>0.0004076070836833262</v>
       </c>
       <c r="AU5" t="n">
         <v>0.0004501973381811802</v>
@@ -2602,19 +2602,19 @@
         <v>0.04242332322754325</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0009237582461756403</v>
+        <v>0.0009237582461756404</v>
       </c>
       <c r="BA5" t="n">
         <v>0.0003504341656519024</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.04970071869356309</v>
+        <v>0.04970071869356307</v>
       </c>
       <c r="BC5" t="n">
         <v>0.01699034814319229</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0142323750660225</v>
+        <v>0.01423237506602249</v>
       </c>
       <c r="BE5" t="n">
         <v>0.001968871332883028</v>
@@ -2623,13 +2623,13 @@
         <v>0.001938598779796693</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.00210580970976458</v>
+        <v>0.002105809709764581</v>
       </c>
       <c r="BH5" t="n">
         <v>0.0120967276360296</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0008215106944706929</v>
+        <v>0.0008215106944706927</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.0006734091009884978</v>
@@ -2650,10 +2650,10 @@
         <v>0.0001318629113914031</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0006623592011591605</v>
+        <v>0.0006623592011591604</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0009088260020386009</v>
+        <v>0.0009088260020386011</v>
       </c>
       <c r="BR5" t="n">
         <v>0.001047774664491028</v>
@@ -2665,7 +2665,7 @@
         <v>0.00609738541870462</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.006388019538184302</v>
+        <v>0.0063880195381843</v>
       </c>
       <c r="BV5" t="n">
         <v>0.005457372397157169</v>
@@ -2683,7 +2683,7 @@
         <v>0.0328832015237966</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002977600190888229</v>
+        <v>0.000297760019088823</v>
       </c>
       <c r="CB5" t="n">
         <v>0.0005591171342998268</v>
@@ -2710,7 +2710,7 @@
         <v>0.0003780408767394108</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.01995775802250916</v>
+        <v>0.01995775802250917</v>
       </c>
       <c r="CK5" t="n">
         <v>5.84126846243014e-05</v>
@@ -2719,16 +2719,16 @@
         <v>0.001846873854393551</v>
       </c>
       <c r="CM5" t="n">
-        <v>6.473508601487339e-05</v>
+        <v>6.47350860148734e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0004739921332973538</v>
+        <v>0.0004739921332973537</v>
       </c>
       <c r="CO5" t="n">
         <v>0.0007008468417436651</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0009210197912092952</v>
+        <v>0.000921019791209295</v>
       </c>
       <c r="CQ5" t="n">
         <v>0.001149695929625199</v>
@@ -2740,7 +2740,7 @@
         <v>0.0001477681325461929</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0005695903514442229</v>
+        <v>0.000569590351444223</v>
       </c>
       <c r="CU5" t="n">
         <v>0.0002858684581424492</v>
@@ -2752,7 +2752,7 @@
         <v>0.000518748103453611</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.004945121414306791</v>
+        <v>0.004945121414306792</v>
       </c>
       <c r="CY5" t="n">
         <v>0.0002425502502102747</v>
@@ -2764,19 +2764,19 @@
         <v>0.001133466867728372</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0009449521164497784</v>
+        <v>0.0009449521164497786</v>
       </c>
       <c r="DC5" t="n">
         <v>6.605602595483235e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.00310258628005581</v>
+        <v>0.003102586280055811</v>
       </c>
       <c r="DE5" t="n">
         <v>0.000192282630077617</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.00212260370479373</v>
+        <v>0.002122603704793731</v>
       </c>
       <c r="DG5" t="n">
         <v>0.01246474870797617</v>
@@ -2797,7 +2797,7 @@
         <v>0.0004506958442220006</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0008976703429479456</v>
+        <v>0.0008976703429479457</v>
       </c>
       <c r="DN5" t="n">
         <v>5.830078129464113e-05</v>
@@ -2806,7 +2806,7 @@
         <v>0.00261247536931393</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.09524181228279194</v>
+        <v>0.09524181228279197</v>
       </c>
       <c r="DQ5" t="n">
         <v>3.758540001701815e-05</v>
@@ -2857,13 +2857,13 @@
         <v>2.595979058028602e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0003566778386815545</v>
+        <v>0.0003566778386815546</v>
       </c>
       <c r="EH5" t="n">
         <v>0.000161701156740526</v>
       </c>
       <c r="EI5" t="n">
-        <v>8.509439043525174e-05</v>
+        <v>8.509439043525172e-05</v>
       </c>
       <c r="EJ5" t="n">
         <v>6.092891867995924e-05</v>
@@ -2887,25 +2887,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5299345748921442</v>
+        <v>0.529934574892144</v>
       </c>
       <c r="C6" t="n">
         <v>0.002052522295729635</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002747703936886788</v>
+        <v>0.002747703936886787</v>
       </c>
       <c r="E6" t="n">
         <v>0.05311555413821412</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2597610983239371</v>
+        <v>0.2597610983239375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7354167727618759</v>
+        <v>0.735416772761875</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2500945290249986</v>
+        <v>0.2500945290249987</v>
       </c>
       <c r="I6" t="n">
         <v>0.01882724461164284</v>
@@ -2917,13 +2917,13 @@
         <v>0.01487235815127472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07654208226067591</v>
+        <v>0.07654208226067592</v>
       </c>
       <c r="M6" t="n">
         <v>0.01897304135694425</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02722883903532965</v>
+        <v>0.02722883903532964</v>
       </c>
       <c r="O6" t="n">
         <v>0.003321018454892488</v>
@@ -2938,7 +2938,7 @@
         <v>0.01120296569583824</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009966703201301724</v>
+        <v>0.009966703201301722</v>
       </c>
       <c r="T6" t="n">
         <v>0.03304916023300448</v>
@@ -2956,19 +2956,19 @@
         <v>0.0003488135006925976</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.004787929336587385</v>
+        <v>0.004787929336587384</v>
       </c>
       <c r="Z6" t="n">
         <v>0.008182569425873228</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02704689096483576</v>
+        <v>0.02704689096483577</v>
       </c>
       <c r="AB6" t="n">
         <v>0.001971094732713696</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.09473253722403055</v>
+        <v>0.09473253722403061</v>
       </c>
       <c r="AD6" t="n">
         <v>0.0001012075968074319</v>
@@ -2977,13 +2977,13 @@
         <v>4.906307873887535e-05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07433770965146112</v>
+        <v>0.07433770965146114</v>
       </c>
       <c r="AG6" t="n">
         <v>0.0343941024200681</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0040222045488226</v>
+        <v>0.004022204548822598</v>
       </c>
       <c r="AI6" t="n">
         <v>0.001312010375700409</v>
@@ -2992,13 +2992,13 @@
         <v>0.004434309592505877</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.03004678029158371</v>
+        <v>0.03004678029158372</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002737020154010111</v>
+        <v>0.00273702015401011</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0005379213799695389</v>
+        <v>0.000537921379969539</v>
       </c>
       <c r="AN6" t="n">
         <v>0.0003878002346536198</v>
@@ -3007,10 +3007,10 @@
         <v>0.002059934837998091</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.001527998949199265</v>
+        <v>0.001527998949199266</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.00413796755640272</v>
+        <v>0.004137967556402721</v>
       </c>
       <c r="AR6" t="n">
         <v>0.009459831609073932</v>
@@ -3019,7 +3019,7 @@
         <v>8.839210526208947e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0004674937417544665</v>
+        <v>0.0004674937417544666</v>
       </c>
       <c r="AU6" t="n">
         <v>0.0005592341863685083</v>
@@ -3034,13 +3034,13 @@
         <v>0.002060400868615999</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.06683035884600763</v>
+        <v>0.06683035884600766</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.001044877016934704</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.000474345848238544</v>
+        <v>0.0004743458482385442</v>
       </c>
       <c r="BB6" t="n">
         <v>0.05013015966437438</v>
@@ -3082,13 +3082,13 @@
         <v>0.003123228311892491</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0001611504078308821</v>
+        <v>0.0001611504078308822</v>
       </c>
       <c r="BP6" t="n">
         <v>0.0007652754105711879</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0009224275781005867</v>
+        <v>0.0009224275781005866</v>
       </c>
       <c r="BR6" t="n">
         <v>0.001584042343902421</v>
@@ -3100,16 +3100,16 @@
         <v>0.008108719038480856</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.008161945297350783</v>
+        <v>0.008161945297350785</v>
       </c>
       <c r="BV6" t="n">
         <v>0.005837382553381109</v>
       </c>
       <c r="BW6" t="n">
-        <v>4.995739128836377e-05</v>
+        <v>4.995739128836376e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.002669198573804052</v>
+        <v>0.002669198573804053</v>
       </c>
       <c r="BY6" t="n">
         <v>0.0008134019364996946</v>
@@ -3166,7 +3166,7 @@
         <v>0.001491023372163032</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.002335390469692889</v>
+        <v>0.00233539046969289</v>
       </c>
       <c r="CR6" t="n">
         <v>0.0006871283703234461</v>
@@ -3184,10 +3184,10 @@
         <v>0.0008906213778691452</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0006960780778165506</v>
+        <v>0.0006960780778165507</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.005287649088268391</v>
+        <v>0.00528764908826839</v>
       </c>
       <c r="CY6" t="n">
         <v>0.0003559164140144523</v>
@@ -3229,10 +3229,10 @@
         <v>0.003120307057979519</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0005140182423785839</v>
+        <v>0.0005140182423785838</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0006048326029876993</v>
+        <v>0.0006048326029876992</v>
       </c>
       <c r="DN6" t="n">
         <v>7.5078812667771e-05</v>
@@ -3256,7 +3256,7 @@
         <v>0.00270208011222918</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.005250713318566989</v>
+        <v>0.005250713318566988</v>
       </c>
       <c r="DV6" t="n">
         <v>0.001173927254818327</v>
@@ -3268,22 +3268,22 @@
         <v>0.001647212024518754</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0003449532390662186</v>
+        <v>0.0003449532390662185</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0006921090278433129</v>
+        <v>0.0006921090278433128</v>
       </c>
       <c r="EA6" t="n">
         <v>0.0008494494444851188</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0007471502133908293</v>
+        <v>0.0007471502133908296</v>
       </c>
       <c r="EC6" t="n">
         <v>0.02245359767817744</v>
       </c>
       <c r="ED6" t="n">
-        <v>5.547178709305567e-05</v>
+        <v>5.547178709305566e-05</v>
       </c>
       <c r="EE6" t="n">
         <v>0.0002852076061572521</v>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5498365034764117</v>
+        <v>0.5498365034764123</v>
       </c>
       <c r="C7" t="n">
         <v>0.002087270898910748</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00281049656662199</v>
+        <v>0.002810496566621991</v>
       </c>
       <c r="E7" t="n">
         <v>0.05844541456430546</v>
@@ -3337,10 +3337,10 @@
         <v>0.257973822620359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7438054494885242</v>
+        <v>0.7438054494885241</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2722809141344964</v>
+        <v>0.2722809141344963</v>
       </c>
       <c r="I7" t="n">
         <v>0.02145273836507618</v>
@@ -3349,34 +3349,34 @@
         <v>0.05106865028768307</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01642078699346756</v>
+        <v>0.01642078699346755</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07864084547411464</v>
+        <v>0.07864084547411467</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01889207816354709</v>
+        <v>0.0188920781635471</v>
       </c>
       <c r="N7" t="n">
         <v>0.02866800017020112</v>
       </c>
       <c r="O7" t="n">
-        <v>0.003852164233230871</v>
+        <v>0.003852164233230872</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01793331838457235</v>
+        <v>0.01793331838457236</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004791354759121534</v>
+        <v>0.004791354759121538</v>
       </c>
       <c r="R7" t="n">
         <v>0.01136827337291785</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0104555118061301</v>
+        <v>0.01045551180613011</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03554256159213796</v>
+        <v>0.03554256159213797</v>
       </c>
       <c r="U7" t="n">
         <v>0.0002339038757284055</v>
@@ -3385,34 +3385,34 @@
         <v>0.002815064995174248</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0208429174845369</v>
+        <v>0.02084291748453691</v>
       </c>
       <c r="X7" t="n">
         <v>0.0003599196813164501</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005117893676660294</v>
+        <v>0.005117893676660296</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008113054679726532</v>
+        <v>0.008113054679726533</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02988480033380326</v>
+        <v>0.02988480033380324</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.002114148642329313</v>
+        <v>0.002114148642329314</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.08743373621801402</v>
+        <v>0.08743373621801406</v>
       </c>
       <c r="AD7" t="n">
         <v>0.000101555640688846</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.228969246323984e-05</v>
+        <v>5.228969246323985e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.07935642952320011</v>
+        <v>0.07935642952320016</v>
       </c>
       <c r="AG7" t="n">
         <v>0.03779816440700071</v>
@@ -3424,13 +3424,13 @@
         <v>0.001433308977870862</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004689226111695494</v>
+        <v>0.004689226111695493</v>
       </c>
       <c r="AK7" t="n">
         <v>0.03167848379216123</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.00277129154710259</v>
+        <v>0.002771291547102591</v>
       </c>
       <c r="AM7" t="n">
         <v>0.0005094361650311694</v>
@@ -3445,10 +3445,10 @@
         <v>0.001597548719730897</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.004869451527405145</v>
+        <v>0.004869451527405147</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.009926880235855744</v>
+        <v>0.009926880235855742</v>
       </c>
       <c r="AS7" t="n">
         <v>9.168524798250091e-05</v>
@@ -3463,13 +3463,13 @@
         <v>0.00326873929005181</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.03160813167020438</v>
+        <v>0.03160813167020439</v>
       </c>
       <c r="AX7" t="n">
         <v>0.002086870033959053</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.06819016121969311</v>
+        <v>0.0681901612196931</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.001116206258971869</v>
@@ -3478,13 +3478,13 @@
         <v>0.0004604278337404661</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.05378662633875941</v>
+        <v>0.05378662633875942</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0182886452418531</v>
+        <v>0.01828864524185311</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0274549510030536</v>
+        <v>0.02745495100305361</v>
       </c>
       <c r="BE7" t="n">
         <v>0.002249426023151747</v>
@@ -3496,10 +3496,10 @@
         <v>0.002905578030942122</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.01510053891192218</v>
+        <v>0.01510053891192217</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0009234928852318333</v>
+        <v>0.0009234928852318332</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.001119160970588171</v>
@@ -3508,16 +3508,16 @@
         <v>0.01382548008663522</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.00028267135169167</v>
+        <v>0.0002826713516916699</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04653094061048648</v>
+        <v>0.04653094061048647</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.003266894744771806</v>
+        <v>0.003266894744771807</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001563517965014188</v>
+        <v>0.0001563517965014187</v>
       </c>
       <c r="BP7" t="n">
         <v>0.0008057069611352637</v>
@@ -3529,7 +3529,7 @@
         <v>0.001320333831176707</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.01720138981481681</v>
+        <v>0.01720138981481682</v>
       </c>
       <c r="BT7" t="n">
         <v>0.009167781418569682</v>
@@ -3541,10 +3541,10 @@
         <v>0.006372868541341049</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.861100961586715e-05</v>
+        <v>5.861100961586716e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002796776490882463</v>
+        <v>0.002796776490882464</v>
       </c>
       <c r="BY7" t="n">
         <v>0.0009020314389858369</v>
@@ -3556,13 +3556,13 @@
         <v>0.0003980458376690638</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0006353970761973707</v>
+        <v>0.0006353970761973708</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0002646866427041028</v>
+        <v>0.0002646866427041027</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.000635999116336758</v>
+        <v>0.0006359991163367579</v>
       </c>
       <c r="CE7" t="n">
         <v>0.01245843541731129</v>
@@ -3571,7 +3571,7 @@
         <v>0.001626783481283952</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01412363331936931</v>
+        <v>0.0141236333193693</v>
       </c>
       <c r="CH7" t="n">
         <v>0.001380885892498201</v>
@@ -3592,10 +3592,10 @@
         <v>0.0001110568462749759</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0006310580384247216</v>
+        <v>0.0006310580384247217</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0008397736076490932</v>
+        <v>0.0008397736076490933</v>
       </c>
       <c r="CP7" t="n">
         <v>0.001433726799031664</v>
@@ -3613,7 +3613,7 @@
         <v>0.0008891536705997459</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0005796830832752918</v>
+        <v>0.0005796830832752919</v>
       </c>
       <c r="CV7" t="n">
         <v>0.0009348816748506264</v>
@@ -3658,13 +3658,13 @@
         <v>0.0001799903646665327</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0004435784266270908</v>
+        <v>0.0004435784266270909</v>
       </c>
       <c r="DK7" t="n">
         <v>0.003531578682380606</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0005344276298555598</v>
+        <v>0.0005344276298555597</v>
       </c>
       <c r="DM7" t="n">
         <v>0.0008632836287606963</v>
@@ -3673,7 +3673,7 @@
         <v>7.481891910510263e-05</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.004567702552234477</v>
+        <v>0.004567702552234479</v>
       </c>
       <c r="DP7" t="n">
         <v>0.1474095982813083</v>
@@ -3691,7 +3691,7 @@
         <v>0.00247929098403433</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.005180360579241638</v>
+        <v>0.005180360579241637</v>
       </c>
       <c r="DV7" t="n">
         <v>0.00119256822636381</v>
@@ -3718,7 +3718,7 @@
         <v>0.02280775730296472</v>
       </c>
       <c r="ED7" t="n">
-        <v>5.430274172831245e-05</v>
+        <v>5.430274172831246e-05</v>
       </c>
       <c r="EE7" t="n">
         <v>0.0002901622116690434</v>
@@ -3727,7 +3727,7 @@
         <v>3.495848599844757e-05</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0004733129871558357</v>
+        <v>0.0004733129871558358</v>
       </c>
       <c r="EH7" t="n">
         <v>0.0002153518739168433</v>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3224824066495273</v>
+        <v>0.3224824066495272</v>
       </c>
       <c r="C8" t="n">
         <v>0.001242197792708662</v>
@@ -3772,10 +3772,10 @@
         <v>0.1521324908624405</v>
       </c>
       <c r="G8" t="n">
-        <v>0.447035899276611</v>
+        <v>0.4470358992766111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1623253700870058</v>
+        <v>0.1623253700870056</v>
       </c>
       <c r="I8" t="n">
         <v>0.01164804599945487</v>
@@ -3784,7 +3784,7 @@
         <v>0.02937213074997121</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009399903997977577</v>
+        <v>0.009399903997977575</v>
       </c>
       <c r="L8" t="n">
         <v>0.04669290578964694</v>
@@ -3793,7 +3793,7 @@
         <v>0.01157946910150908</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01752511522591681</v>
+        <v>0.01752511522591682</v>
       </c>
       <c r="O8" t="n">
         <v>0.002447592931140784</v>
@@ -3805,19 +3805,19 @@
         <v>0.002786718522644208</v>
       </c>
       <c r="R8" t="n">
-        <v>0.006459455786842917</v>
+        <v>0.006459455786842914</v>
       </c>
       <c r="S8" t="n">
         <v>0.006038833177869958</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01894994676672049</v>
+        <v>0.01894994676672051</v>
       </c>
       <c r="U8" t="n">
         <v>0.0001407989612484488</v>
       </c>
       <c r="V8" t="n">
-        <v>0.001693966340509162</v>
+        <v>0.001693966340509163</v>
       </c>
       <c r="W8" t="n">
         <v>0.01332291756618704</v>
@@ -3826,10 +3826,10 @@
         <v>0.0001994819977656761</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002841879631855977</v>
+        <v>0.002841879631855976</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004638300344483265</v>
+        <v>0.004638300344483264</v>
       </c>
       <c r="AA8" t="n">
         <v>0.01764582845156708</v>
@@ -3838,10 +3838,10 @@
         <v>0.001239633943453578</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05368801768315602</v>
+        <v>0.053688017683156</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.867675502352839e-05</v>
+        <v>5.867675502352838e-05</v>
       </c>
       <c r="AE8" t="n">
         <v>3.098094687305592e-05</v>
@@ -3865,7 +3865,7 @@
         <v>0.01647358292721865</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001568137721066568</v>
+        <v>0.001568137721066569</v>
       </c>
       <c r="AM8" t="n">
         <v>0.0003060512920627237</v>
@@ -3874,7 +3874,7 @@
         <v>0.0002438048376197232</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001275424127968762</v>
+        <v>0.001275424127968763</v>
       </c>
       <c r="AP8" t="n">
         <v>0.0009659948871630072</v>
@@ -3883,13 +3883,13 @@
         <v>0.002722844943801619</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.005812349104038784</v>
+        <v>0.005812349104038782</v>
       </c>
       <c r="AS8" t="n">
         <v>5.547814050348534e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0002792472210710255</v>
+        <v>0.0002792472210710254</v>
       </c>
       <c r="AU8" t="n">
         <v>0.000349031745384101</v>
@@ -3907,13 +3907,13 @@
         <v>0.03764280843651707</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0007596783446968597</v>
+        <v>0.0007596783446968599</v>
       </c>
       <c r="BA8" t="n">
         <v>0.0002679094589926523</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0335717155862528</v>
+        <v>0.03357171558625282</v>
       </c>
       <c r="BC8" t="n">
         <v>0.01097549205122549</v>
@@ -3922,7 +3922,7 @@
         <v>0.0127574213766017</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001445177507901859</v>
+        <v>0.00144517750790186</v>
       </c>
       <c r="BF8" t="n">
         <v>0.00126213297454342</v>
@@ -3934,19 +3934,19 @@
         <v>0.009564491336446287</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.000592216956185619</v>
+        <v>0.0005922169561856189</v>
       </c>
       <c r="BJ8" t="n">
         <v>0.0005733084128010694</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.008710621474147293</v>
+        <v>0.008710621474147286</v>
       </c>
       <c r="BL8" t="n">
         <v>0.0001616149611932084</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.02517366824811882</v>
+        <v>0.02517366824811881</v>
       </c>
       <c r="BN8" t="n">
         <v>0.001843353817270963</v>
@@ -3967,7 +3967,7 @@
         <v>0.01104964306908993</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.00466860043280085</v>
+        <v>0.004668600432800849</v>
       </c>
       <c r="BU8" t="n">
         <v>0.005038264794166815</v>
@@ -3976,7 +3976,7 @@
         <v>0.003791194607554259</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.867249218880422e-05</v>
+        <v>2.867249218880423e-05</v>
       </c>
       <c r="BX8" t="n">
         <v>0.001642898520930329</v>
@@ -3988,16 +3988,16 @@
         <v>0.02673056287782778</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0002294778551166658</v>
+        <v>0.0002294778551166659</v>
       </c>
       <c r="CB8" t="n">
         <v>0.0004049105400889481</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0001626133740690692</v>
+        <v>0.0001626133740690691</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0003120186526591517</v>
+        <v>0.0003120186526591516</v>
       </c>
       <c r="CE8" t="n">
         <v>0.008000316364526182</v>
@@ -4006,10 +4006,10 @@
         <v>0.001021395072856708</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.008843466648192659</v>
+        <v>0.00884346664819266</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0008866524613502471</v>
+        <v>0.000886652461350247</v>
       </c>
       <c r="CI8" t="n">
         <v>0.0001601249081986631</v>
@@ -4024,7 +4024,7 @@
         <v>0.001342569985988429</v>
       </c>
       <c r="CM8" t="n">
-        <v>4.975013327154168e-05</v>
+        <v>4.975013327154167e-05</v>
       </c>
       <c r="CN8" t="n">
         <v>0.0003610304352502873</v>
@@ -4033,7 +4033,7 @@
         <v>0.0005773422001504707</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0006960681621411196</v>
+        <v>0.0006960681621411197</v>
       </c>
       <c r="CQ8" t="n">
         <v>0.001097953796464779</v>
@@ -4072,10 +4072,10 @@
         <v>0.0007057263057469818</v>
       </c>
       <c r="DC8" t="n">
-        <v>5.623814756304434e-05</v>
+        <v>5.623814756304433e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002493301695519587</v>
+        <v>0.002493301695519586</v>
       </c>
       <c r="DE8" t="n">
         <v>0.0001497527292988786</v>
@@ -4084,7 +4084,7 @@
         <v>0.001534226153400127</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.00769568388492715</v>
+        <v>0.007695683884927151</v>
       </c>
       <c r="DH8" t="n">
         <v>0.001417531074534073</v>
@@ -4111,25 +4111,25 @@
         <v>0.002282621296694471</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.08403632211407107</v>
+        <v>0.0840363221140711</v>
       </c>
       <c r="DQ8" t="n">
-        <v>2.808987432740122e-05</v>
+        <v>2.808987432740123e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001085845380413202</v>
+        <v>0.0001085845380413203</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.001753971152354448</v>
+        <v>0.001753971152354447</v>
       </c>
       <c r="DT8" t="n">
         <v>0.001370349897257407</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.002957778103543684</v>
+        <v>0.002957778103543683</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0006529475512652217</v>
+        <v>0.0006529475512652216</v>
       </c>
       <c r="DW8" t="n">
         <v>0.001108470872710505</v>
@@ -4159,7 +4159,7 @@
         <v>0.0001476817191054994</v>
       </c>
       <c r="EF8" t="n">
-        <v>2.013353447173935e-05</v>
+        <v>2.013353447173936e-05</v>
       </c>
       <c r="EG8" t="n">
         <v>0.000270255456011825</v>
@@ -4168,7 +4168,7 @@
         <v>0.0001278882414460017</v>
       </c>
       <c r="EI8" t="n">
-        <v>6.808154941382402e-05</v>
+        <v>6.808154941382403e-05</v>
       </c>
       <c r="EJ8" t="n">
         <v>4.626614608188856e-05</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3436030939561711</v>
+        <v>0.3436030939561709</v>
       </c>
       <c r="C9" t="n">
         <v>0.001357810167937169</v>
@@ -4204,13 +4204,13 @@
         <v>0.03718011790524389</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1713058781983859</v>
+        <v>0.1713058781983858</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4572292602392647</v>
+        <v>0.4572292602392652</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1812455655763622</v>
+        <v>0.1812455655763623</v>
       </c>
       <c r="I9" t="n">
         <v>0.01551846118898776</v>
@@ -4219,10 +4219,10 @@
         <v>0.03021513656359232</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01234036595382299</v>
+        <v>0.012340365953823</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04942551323212097</v>
+        <v>0.049425513232121</v>
       </c>
       <c r="M9" t="n">
         <v>0.01186969215487272</v>
@@ -4231,7 +4231,7 @@
         <v>0.01919433906531262</v>
       </c>
       <c r="O9" t="n">
-        <v>0.002603928469516502</v>
+        <v>0.002603928469516503</v>
       </c>
       <c r="P9" t="n">
         <v>0.01100274219344514</v>
@@ -4243,10 +4243,10 @@
         <v>0.007074824289377802</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006743842536240283</v>
+        <v>0.006743842536240285</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02110677083946469</v>
+        <v>0.02110677083946467</v>
       </c>
       <c r="U9" t="n">
         <v>0.0001412851889868535</v>
@@ -4258,13 +4258,13 @@
         <v>0.01413056800335174</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0002072870055920971</v>
+        <v>0.0002072870055920972</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003263107281701314</v>
+        <v>0.003263107281701315</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004785109183876045</v>
+        <v>0.004785109183876044</v>
       </c>
       <c r="AA9" t="n">
         <v>0.01641213128614903</v>
@@ -4273,7 +4273,7 @@
         <v>0.001262290025432175</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05589105076963585</v>
+        <v>0.05589105076963583</v>
       </c>
       <c r="AD9" t="n">
         <v>5.897603557607187e-05</v>
@@ -4282,7 +4282,7 @@
         <v>2.922848646382211e-05</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.04542680898001226</v>
+        <v>0.04542680898001224</v>
       </c>
       <c r="AG9" t="n">
         <v>0.03127020992059677</v>
@@ -4291,13 +4291,13 @@
         <v>0.002819562939157047</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001045215912405165</v>
+        <v>0.001045215912405166</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002723558143193919</v>
+        <v>0.002723558143193918</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01832972921972575</v>
+        <v>0.01832972921972574</v>
       </c>
       <c r="AL9" t="n">
         <v>0.001624610963324564</v>
@@ -4309,7 +4309,7 @@
         <v>0.0002964771009169858</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001485119277915442</v>
+        <v>0.001485119277915443</v>
       </c>
       <c r="AP9" t="n">
         <v>0.001107415822511123</v>
@@ -4318,7 +4318,7 @@
         <v>0.003542963793128389</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.005969006125607702</v>
+        <v>0.005969006125607701</v>
       </c>
       <c r="AS9" t="n">
         <v>5.82519324332952e-05</v>
@@ -4333,13 +4333,13 @@
         <v>0.002780443381926618</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01777785125531894</v>
+        <v>0.01777785125531895</v>
       </c>
       <c r="AX9" t="n">
         <v>0.001141280828365575</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03423900230091094</v>
+        <v>0.03423900230091093</v>
       </c>
       <c r="AZ9" t="n">
         <v>0.0007230429567978425</v>
@@ -4348,7 +4348,7 @@
         <v>0.0002699688905173946</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.03855418436262799</v>
+        <v>0.03855418436262798</v>
       </c>
       <c r="BC9" t="n">
         <v>0.01276953653545165</v>
@@ -4366,31 +4366,31 @@
         <v>0.001711209829760501</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.009733931060641242</v>
+        <v>0.009733931060641243</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0006712524231893297</v>
+        <v>0.0006712524231893296</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.0005640805295265376</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.009985327648659396</v>
+        <v>0.009985327648659399</v>
       </c>
       <c r="BL9" t="n">
         <v>0.0002121567561215569</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.02609036227087152</v>
+        <v>0.02609036227087153</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002150747821755039</v>
+        <v>0.002150747821755038</v>
       </c>
       <c r="BO9" t="n">
         <v>0.0001024286850388606</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0005113790434673136</v>
+        <v>0.0005113790434673137</v>
       </c>
       <c r="BQ9" t="n">
         <v>0.0007089059283655135</v>
@@ -4402,13 +4402,13 @@
         <v>0.01241404671556724</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005076106647535062</v>
+        <v>0.005076106647535061</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.005625032049677993</v>
+        <v>0.005625032049677992</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.004463965983382726</v>
+        <v>0.004463965983382725</v>
       </c>
       <c r="BW9" t="n">
         <v>4.13275609000788e-05</v>
@@ -4441,13 +4441,13 @@
         <v>0.001136787605346194</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009207433104408648</v>
+        <v>0.009207433104408644</v>
       </c>
       <c r="CH9" t="n">
         <v>0.0008629487862571331</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0003352688545851673</v>
+        <v>0.0003352688545851672</v>
       </c>
       <c r="CJ9" t="n">
         <v>0.01552818557584068</v>
@@ -4462,16 +4462,16 @@
         <v>5.460233473917781e-05</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0003672657018103567</v>
+        <v>0.0003672657018103568</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.000514055075109339</v>
+        <v>0.0005140550751093391</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0007701658318890083</v>
+        <v>0.0007701658318890082</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.00130162368019252</v>
+        <v>0.001301623680192521</v>
       </c>
       <c r="CR9" t="n">
         <v>0.0004695385815555212</v>
@@ -4498,7 +4498,7 @@
         <v>0.0001943882112391087</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004712343158943529</v>
+        <v>0.000471234315894353</v>
       </c>
       <c r="DA9" t="n">
         <v>0.0009963581622997369</v>
@@ -4507,7 +4507,7 @@
         <v>0.0007484147570008195</v>
       </c>
       <c r="DC9" t="n">
-        <v>5.551423499854828e-05</v>
+        <v>5.551423499854829e-05</v>
       </c>
       <c r="DD9" t="n">
         <v>0.002411899391835818</v>
@@ -4546,7 +4546,7 @@
         <v>0.002309389974654582</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.07630067143219157</v>
+        <v>0.07630067143219162</v>
       </c>
       <c r="DQ9" t="n">
         <v>2.940536967602855e-05</v>
@@ -4564,7 +4564,7 @@
         <v>0.003055798415797824</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0006553086988506286</v>
+        <v>0.0006553086988506287</v>
       </c>
       <c r="DW9" t="n">
         <v>0.001048041498308906</v>
@@ -4576,7 +4576,7 @@
         <v>0.0002153248561332576</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0004156891397307702</v>
+        <v>0.0004156891397307701</v>
       </c>
       <c r="EA9" t="n">
         <v>0.0004701242750660571</v>
@@ -4588,7 +4588,7 @@
         <v>0.01203598438803701</v>
       </c>
       <c r="ED9" t="n">
-        <v>3.315933662700297e-05</v>
+        <v>3.315933662700296e-05</v>
       </c>
       <c r="EE9" t="n">
         <v>0.0001425529953827135</v>
@@ -4603,7 +4603,7 @@
         <v>0.0001305116676293152</v>
       </c>
       <c r="EI9" t="n">
-        <v>6.496155582017061e-05</v>
+        <v>6.49615558201706e-05</v>
       </c>
       <c r="EJ9" t="n">
         <v>4.784565404901558e-05</v>
